--- a/docs/seed-data/golden-source-final-v6.xlsx
+++ b/docs/seed-data/golden-source-final-v6.xlsx
@@ -15,8 +15,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Subprocess Order'!A1:I28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Step Evolution'!A1:K222</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">'Scope Matrix'!A1:AB18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'ADHOC (Removed)'!A1:F124</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5">'Still Unmapped'!A1:E18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'ADHOC (Removed)'!A1:F125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5">'Still Unmapped'!A1:E32</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -45,9 +45,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;_-* \(#,##0.00\)_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -490,7 +489,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="str">
-        <v>1.02</v>
+        <v>1.00</v>
       </c>
       <c r="K2" t="str">
         <v>Delete_Portfolio_AU_MCP</v>
@@ -525,7 +524,7 @@
         <v>2</v>
       </c>
       <c r="J3" t="str">
-        <v>2.02</v>
+        <v>2.00</v>
       </c>
       <c r="K3" t="str">
         <v>Load_compare_MP_AU_MCP</v>
@@ -560,7 +559,7 @@
         <v>2</v>
       </c>
       <c r="J4" t="str">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="K4" t="str">
         <v>Load_compare_Spreads_AU_MCP</v>
@@ -595,7 +594,7 @@
         <v>4</v>
       </c>
       <c r="J5" t="str">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="K5" t="str">
         <v>Load_POS_AU_MCP</v>
@@ -630,7 +629,7 @@
         <v>6</v>
       </c>
       <c r="J6" t="str">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="K6" t="str">
         <v>Valuation_AU_MCP</v>
@@ -665,7 +664,7 @@
         <v>3</v>
       </c>
       <c r="J7" t="str">
-        <v>6.77</v>
+        <v>6.75</v>
       </c>
       <c r="K7" t="str">
         <v>CSRBB_Valuation_AU_MCP</v>
@@ -700,7 +699,7 @@
         <v>6</v>
       </c>
       <c r="J8" t="str">
-        <v>8.31</v>
+        <v>8.29</v>
       </c>
       <c r="K8" t="str">
         <v>CSRBB_Planning_AU_MCP</v>
@@ -735,7 +734,7 @@
         <v>4</v>
       </c>
       <c r="J9" t="str">
-        <v>8.38</v>
+        <v>8.36</v>
       </c>
       <c r="K9" t="str">
         <v>EC_AU_MCP</v>
@@ -770,7 +769,7 @@
         <v>4</v>
       </c>
       <c r="J10" t="str">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="K10" t="str">
         <v>KR_AU_MCP, KR_AU_MCP rr due to tech issue, KR_AU_MCP_rr</v>
@@ -805,10 +804,10 @@
         <v>1</v>
       </c>
       <c r="J11" t="str">
-        <v>10.12</v>
+        <v>10.10</v>
       </c>
       <c r="K11" t="str">
-        <v>Import_Strategies_AU_MCP, Import_Strategies_AU_MCP rr , Import_Strategies_AU_MCP import updated strategies</v>
+        <v>Import_Strategies_AU_MCP, Import_Strategies_AU_MCP rr, Import_Strategies_AU_MCP import updated strategies</v>
       </c>
     </row>
     <row r="12">
@@ -840,7 +839,7 @@
         <v>6</v>
       </c>
       <c r="J12" t="str">
-        <v>10.63</v>
+        <v>10.90</v>
       </c>
       <c r="K12" t="str">
         <v>Planning_AU_MCP</v>
@@ -875,7 +874,7 @@
         <v>3</v>
       </c>
       <c r="J13" t="str">
-        <v>11.14</v>
+        <v>11.11</v>
       </c>
       <c r="K13" t="str">
         <v>ITS_AU_MCP</v>
@@ -910,7 +909,7 @@
         <v>2</v>
       </c>
       <c r="J14" t="str">
-        <v>11.39</v>
+        <v>11.35</v>
       </c>
       <c r="K14" t="str">
         <v>Valuation_AIC_AU_MCP</v>
@@ -945,7 +944,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="str">
-        <v>1.02</v>
+        <v>1.00</v>
       </c>
       <c r="K15" t="str">
         <v>Delete_Portfolio_BE_MCP, Delete_Portfolio_MCP</v>
@@ -980,7 +979,7 @@
         <v>2</v>
       </c>
       <c r="J16" t="str">
-        <v>2.02</v>
+        <v>2.00</v>
       </c>
       <c r="K16" t="str">
         <v>Load_MP_ATTRIB_BE_MCP, Load_compare_MP_BE_MCP, Load_MP_MCP</v>
@@ -1015,7 +1014,7 @@
         <v>2</v>
       </c>
       <c r="J17" t="str">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="K17" t="str">
         <v>Load_compare_Spreads_ATTRIB_BE_MCP, Load_compare_Spreads_BE_MCP, Load_Spreads_MCP</v>
@@ -1050,7 +1049,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="str">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="K18" t="str">
         <v>Load_POS_ATTRIB_BE_MCP, Load_POS_BE_MCP, Load_POS_MCP</v>
@@ -1085,7 +1084,7 @@
         <v>8</v>
       </c>
       <c r="J19" t="str">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="K19" t="str">
         <v>Valuation_BE_MCP, Valuation_MCP, Valuation_MCP ara, Valuation_MCP_Export</v>
@@ -1120,7 +1119,7 @@
         <v>3</v>
       </c>
       <c r="J20" t="str">
-        <v>8.38</v>
+        <v>8.36</v>
       </c>
       <c r="K20" t="str">
         <v>EC_BE_MCP, EC_BE_MCP rr, EC_MCP, EC_NPV_Export</v>
@@ -1155,7 +1154,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="str">
-        <v>8.74</v>
+        <v>8.72</v>
       </c>
       <c r="K21" t="str">
         <v>GAP_BE_MCP, GAP_BE_MCP rr, GAP_MCP</v>
@@ -1190,7 +1189,7 @@
         <v>4</v>
       </c>
       <c r="J22" t="str">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="K22" t="str">
         <v>KR_BE_MCP, KR_BPV_Export, KR_MCP</v>
@@ -1225,7 +1224,7 @@
         <v>2</v>
       </c>
       <c r="J23" t="str">
-        <v>10.12</v>
+        <v>10.10</v>
       </c>
       <c r="K23" t="str">
         <v>Import_Strategies_BE_MCP, Import_Strategies_Risk_MCP</v>
@@ -1260,7 +1259,7 @@
         <v>8</v>
       </c>
       <c r="J24" t="str">
-        <v>10.63</v>
+        <v>10.90</v>
       </c>
       <c r="K24" t="str">
         <v>Combined_Planning_BE_MCP, Combined_Planning_BE_MCP (rr for missing scen IR_S120_CR_Up), Planning_MCP, Planning_MCP BE rr only missing scenario, Planning_MCP BE rr only missing scenario rr, Planning_MCP_Export, Planning_MCP_Export BE with the rerun, Planning_MCP BE RR</v>
@@ -1295,7 +1294,7 @@
         <v>2</v>
       </c>
       <c r="J25" t="str">
-        <v>11.39</v>
+        <v>11.35</v>
       </c>
       <c r="K25" t="str">
         <v>Valuation_AIC_BE_MCP, Valuation_AIC_MCP</v>
@@ -1400,7 +1399,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="str">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="K28" t="str">
         <v>Load_POS_BEGT_MCP</v>
@@ -1435,7 +1434,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="str">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="K29" t="str">
         <v>Valuation_BEGT_MCP</v>
@@ -1470,7 +1469,7 @@
         <v>5</v>
       </c>
       <c r="J30" t="str">
-        <v>6.77</v>
+        <v>6.75</v>
       </c>
       <c r="K30" t="str">
         <v>CSRBB_Valuation_BEGT_MCP, CSRBB_Valuation_BEGT_MCP (rr), CSRBB_Valuation_Qtr_BEGT_MCP, CSRBB_Valuation_BEGT_MCP rr (INC14661577)</v>
@@ -1505,7 +1504,7 @@
         <v>5</v>
       </c>
       <c r="J31" t="str">
-        <v>8.31</v>
+        <v>8.29</v>
       </c>
       <c r="K31" t="str">
         <v>CSRBB_Planning_BEGT_MCP (run from line 42 down), CSRBB_Planning_BEGT_MCP (run only to set defaults line 38, CSRBB_Planning_Qtr_BEGT_MCP, CSRBB_Planning_BEGT_MCP</v>
@@ -1540,7 +1539,7 @@
         <v>5</v>
       </c>
       <c r="J32" t="str">
-        <v>8.38</v>
+        <v>8.36</v>
       </c>
       <c r="K32" t="str">
         <v>EC_BEGT_MCP</v>
@@ -1575,7 +1574,7 @@
         <v>1</v>
       </c>
       <c r="J33" t="str">
-        <v>8.74</v>
+        <v>8.72</v>
       </c>
       <c r="K33" t="str">
         <v>GAP_BEGT_MCP, GAP_BEGT_MCP rr, GAP_BEGT_MCP rr2 (INC14485851), GAP_BEGT_MCP rr (Export)</v>
@@ -1610,7 +1609,7 @@
         <v>5</v>
       </c>
       <c r="J34" t="str">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="K34" t="str">
         <v>KR_BEGT_MCP</v>
@@ -1645,7 +1644,7 @@
         <v>1</v>
       </c>
       <c r="J35" t="str">
-        <v>10.12</v>
+        <v>10.10</v>
       </c>
       <c r="K35" t="str">
         <v>Import_Strategies_BEGT_MCP, Import_Strategies_BEGT_MCP (rr Run 2), Import_Strategies_BEGT_MCP rr</v>
@@ -1680,7 +1679,7 @@
         <v>6</v>
       </c>
       <c r="J36" t="str">
-        <v>10.63</v>
+        <v>10.90</v>
       </c>
       <c r="K36" t="str">
         <v>Planning_BEGT_MCP_2, Planning_BEGT_MCP_2 (rr Run 2), Planning_BEGT_MCP_2 (rr line 72 down), Planning_BEGT_MCP_2 (Export), Planning_BEGT_MCP_2 rr (Plan run exports), Planning_BEGT_MCP_2 rr INC14661577, Planning_BEGT_MCP_2 rr2 (Plan Run 2), Planning_BEGT_MCP_2 rr3 (Plan run exports), Planning_BEGT_MCP_2 rr4 (PlanRun2 and Export after Manual MDL import)</v>
@@ -1715,7 +1714,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="str">
-        <v>11.14</v>
+        <v>11.11</v>
       </c>
       <c r="K37" t="str">
         <v>ITS_BEGT_MCP</v>
@@ -1785,7 +1784,7 @@
         <v>1</v>
       </c>
       <c r="J39" t="str">
-        <v>1.02</v>
+        <v>1.00</v>
       </c>
       <c r="K39" t="str">
         <v>Delete_Portfolio_DE_MCP, Delete_Portfolio_MCP</v>
@@ -1820,7 +1819,7 @@
         <v>2</v>
       </c>
       <c r="J40" t="str">
-        <v>2.02</v>
+        <v>2.00</v>
       </c>
       <c r="K40" t="str">
         <v>Load_compare_MP_DE_MCP, Load_compare_MP_DE_MCP rr removed import workflow, Load_compare_MP_DE_MCP rr updated workflow path, Load_MP_MCP</v>
@@ -1855,7 +1854,7 @@
         <v>2</v>
       </c>
       <c r="J41" t="str">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="K41" t="str">
         <v>Load_compare_Spreads_DE_MCP, Load_Spreads_MCP</v>
@@ -1890,7 +1889,7 @@
         <v>7</v>
       </c>
       <c r="J42" t="str">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="K42" t="str">
         <v>Load_POS_DE_MCP, Load_POS_MCP, POS_MCP_Export</v>
@@ -1960,7 +1959,7 @@
         <v>9</v>
       </c>
       <c r="J44" t="str">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="K44" t="str">
         <v>Valuation_DE_MCP, Valuation_DE_MCP rerun, new spreads, Valuation_DE_MCP_rr, Valuation_MCP, Valuation_MCP_Export, Valuation_MCP_Export (copy)</v>
@@ -1995,7 +1994,7 @@
         <v>3</v>
       </c>
       <c r="J45" t="str">
-        <v>6.77</v>
+        <v>6.75</v>
       </c>
       <c r="K45" t="str">
         <v>CSRBB_Valuation_DE_MCP, CSRBB_Valuation_Qtr_DE_MCP, CSRBB_Valuation_MCP, CSRBB_Valuation_Qtr_MCP, CSRBB_Valuation_Qtr_MCP_rr after email failure</v>
@@ -2030,7 +2029,7 @@
         <v>5</v>
       </c>
       <c r="J46" t="str">
-        <v>8.31</v>
+        <v>8.29</v>
       </c>
       <c r="K46" t="str">
         <v>CSRBB_Planning_DE_MCP, CSRBB_Planning_DE_MCP rr, CSRBB_Planning_DE_MCP rr 2, CSRBB_Planning_Qtr_DE_MCP</v>
@@ -2065,7 +2064,7 @@
         <v>10</v>
       </c>
       <c r="J47" t="str">
-        <v>8.38</v>
+        <v>8.36</v>
       </c>
       <c r="K47" t="str">
         <v>EC_DE_MCP, EC_MCP</v>
@@ -2100,7 +2099,7 @@
         <v>2</v>
       </c>
       <c r="J48" t="str">
-        <v>8.74</v>
+        <v>8.72</v>
       </c>
       <c r="K48" t="str">
         <v>GAP_DE_MCP, GAP_DE_MCP (copy)</v>
@@ -2135,7 +2134,7 @@
         <v>7</v>
       </c>
       <c r="J49" t="str">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="K49" t="str">
         <v>KR_DE_MCP, KR_DE_MCP rr, KR_DE_MCP rerun, new spreads, KR_MCP Germany, KR_MCP</v>
@@ -2170,7 +2169,7 @@
         <v>4</v>
       </c>
       <c r="J50" t="str">
-        <v>10.12</v>
+        <v>10.10</v>
       </c>
       <c r="K50" t="str">
         <v>Import_Strategies_DE_MCP, Import_Strategies_CBS_MCP, Import_Strategies_Finance_MCP, Import_Strategies_Risk_MCP</v>
@@ -2205,10 +2204,10 @@
         <v>7</v>
       </c>
       <c r="J51" t="str">
-        <v>10.63</v>
+        <v>10.90</v>
       </c>
       <c r="K51" t="str">
-        <v>Planning_DE_MCP , Planning_DE_MCP rr, Planning_DE_MCP rr 2, Planning_DE_MCP rr missing scenarios, Planning_DE_MCP FIN rerun (Export), Planning_DE_MCP csv exports, Planning_MCP, Planning_MCP_Export</v>
+        <v>Planning_DE_MCP , Planning_DE_MCP, Planning_DE_MCP rr, Planning_DE_MCP rr 2, Planning_DE_MCP rr missing scenarios, Planning_DE_MCP FIN rerun (Export), Planning_DE_MCP csv exports, Planning_MCP, Planning_MCP_Export</v>
       </c>
     </row>
     <row r="52">
@@ -2240,7 +2239,7 @@
         <v>3</v>
       </c>
       <c r="J52" t="str">
-        <v>11.14</v>
+        <v>11.11</v>
       </c>
       <c r="K52" t="str">
         <v>ITS_DE_MCP</v>
@@ -2275,7 +2274,7 @@
         <v>2</v>
       </c>
       <c r="J53" t="str">
-        <v>11.39</v>
+        <v>11.35</v>
       </c>
       <c r="K53" t="str">
         <v>Valuation_AIC_DE_MCP</v>
@@ -2450,7 +2449,7 @@
         <v>8</v>
       </c>
       <c r="J58" t="str">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="K58" t="str">
         <v>Load_POS_DEGT_MCP</v>
@@ -2485,7 +2484,7 @@
         <v>6</v>
       </c>
       <c r="J59" t="str">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="K59" t="str">
         <v>Valuation_DEGT_MCP, Valuation_DEGT_MCP (Export)</v>
@@ -2520,7 +2519,7 @@
         <v>1</v>
       </c>
       <c r="J60" t="str">
-        <v>8.74</v>
+        <v>8.72</v>
       </c>
       <c r="K60" t="str">
         <v>GAP_DEGT_MCP, GAP_DEGT_MCP (rr from line 43 down), GAP_DEGT_MCP (rr), GAP_DEGT_MCP rr, GAP_DEGT_MCP rr2 (INC14485851), GAP_DEGT_MCP rr2, GAP_DEGT_MCP rr2 (Export)</v>
@@ -2555,7 +2554,7 @@
         <v>1</v>
       </c>
       <c r="J61" t="str">
-        <v>10.12</v>
+        <v>10.10</v>
       </c>
       <c r="K61" t="str">
         <v>Import_Strategies_DEGT_MCP, Import_Strategies_DEGT_MCP (rr Run 2)</v>
@@ -2590,7 +2589,7 @@
         <v>8</v>
       </c>
       <c r="J62" t="str">
-        <v>10.63</v>
+        <v>10.90</v>
       </c>
       <c r="K62" t="str">
         <v>Planning_DEGT_MCP, Planning_DEGT_MCP_2, Planning_DEGT_MCP_2 (rr after run 1 crash due to primary key viol), Planning_DEGT_MCP_2 (rr export only WF update untick remove unn data), Planning_DEGT_MCP_2 (rr from line 73 down), Planning_DEGT_MCP_2 (rr line 75 down), Planning_DEGT_MCP_2 (rr planning run 2 for S118 and S119), Planning_DEGT_MCP_2 (rr run 2), Planning_DEGT_MCP_2 (rr2 from line 75 down), Planning_DEGT_MCP_2 (rr2 planning run 2 for S118 and S119) , Planning_DEGT_MCP_2 (rr3 due to incorrect comment out in rr), Planning_DEGT_MCP_2 (rr4 from line 84 down), Planning_DEGT_MCP_2 (Export), Planning_DEGT_MCP_2 rr (MDL), Planning_DEGT_MCP_2 rr (missing S118 S119), Planning_DEGT_MCP_2 rr (plan run export), Planning_DEGT_MCP_2 rr2 (missing S118 S119)</v>
@@ -2625,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="J63" t="str">
-        <v>1.02</v>
+        <v>1.00</v>
       </c>
       <c r="K63" t="str">
         <v>Delete_Portfolio_ES_MCP, Delete_Portfolio_MCP</v>
@@ -2660,7 +2659,7 @@
         <v>2</v>
       </c>
       <c r="J64" t="str">
-        <v>2.02</v>
+        <v>2.00</v>
       </c>
       <c r="K64" t="str">
         <v>Load_compare_MP_ES_MCP, Load_MP_MCP, Load_MP_MCP download from papi, Load_MP_MCP rr, Load_MP_MCP rr 2, Load_compare_MP_ES_MCP rr, Load_compare_MP_ES_MCP rr2</v>
@@ -2695,7 +2694,7 @@
         <v>2</v>
       </c>
       <c r="J65" t="str">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="K65" t="str">
         <v>Load_compare_Spreads_ES_MCP, Load_Spreads_MCP, Load_Spreads_MCP RR</v>
@@ -2730,7 +2729,7 @@
         <v>6</v>
       </c>
       <c r="J66" t="str">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="K66" t="str">
         <v>Load_POS_ES_MCP, Load_POS_ES_MCP rr NTG only (capital pos), Load_POS_ES_MCP rr2 stratification+export only, Load_POS_MCP, Load_POS_MCP ntg, POS_MCP_Export</v>
@@ -2765,7 +2764,7 @@
         <v>7</v>
       </c>
       <c r="J67" t="str">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="K67" t="str">
         <v>Valuation_ES_MCP, Valuation_ES_MCP (SOT FX rerun), Valuation_ES_MCP (SOT FX rerun2), Valuation_ES_MCP rr, Valuation_ES_MCP rr2, Valuation_MCP</v>
@@ -2800,7 +2799,7 @@
         <v>4</v>
       </c>
       <c r="J68" t="str">
-        <v>6.77</v>
+        <v>6.75</v>
       </c>
       <c r="K68" t="str">
         <v>CSRBB_Valuation_ES_MCP, CSRBB_Valuation_Qtr_ES_MCP</v>
@@ -2835,7 +2834,7 @@
         <v>5</v>
       </c>
       <c r="J69" t="str">
-        <v>8.31</v>
+        <v>8.29</v>
       </c>
       <c r="K69" t="str">
         <v>CSRBB_Planning_ES_MCP, CSRBB_Planning_Qtr_ES_MCP</v>
@@ -2870,7 +2869,7 @@
         <v>6</v>
       </c>
       <c r="J70" t="str">
-        <v>8.38</v>
+        <v>8.36</v>
       </c>
       <c r="K70" t="str">
         <v>EC_ES_MCP, EC_ES_MCP rr</v>
@@ -2905,7 +2904,7 @@
         <v>1</v>
       </c>
       <c r="J71" t="str">
-        <v>8.74</v>
+        <v>8.72</v>
       </c>
       <c r="K71" t="str">
         <v>GAP_ES_MCP</v>
@@ -2940,7 +2939,7 @@
         <v>5</v>
       </c>
       <c r="J72" t="str">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="K72" t="str">
         <v>KR_ES_MCP</v>
@@ -2975,7 +2974,7 @@
         <v>1</v>
       </c>
       <c r="J73" t="str">
-        <v>10.12</v>
+        <v>10.10</v>
       </c>
       <c r="K73" t="str">
         <v>Import_Strategies_ES_MCP, Import_Strategies_ES_MCP rr for redelivery of Run2 strat</v>
@@ -3010,7 +3009,7 @@
         <v>7</v>
       </c>
       <c r="J74" t="str">
-        <v>10.63</v>
+        <v>10.90</v>
       </c>
       <c r="K74" t="str">
         <v>Planning_ES_MCP, Planning_ES_MCP rr, Planning_ES_MCP rr for redelivery of Run2 strat, Planning_ES_MCP RR</v>
@@ -3045,7 +3044,7 @@
         <v>3</v>
       </c>
       <c r="J75" t="str">
-        <v>11.14</v>
+        <v>11.11</v>
       </c>
       <c r="K75" t="str">
         <v>ITS_ES_MCP</v>
@@ -3080,7 +3079,7 @@
         <v>2</v>
       </c>
       <c r="J76" t="str">
-        <v>11.39</v>
+        <v>11.35</v>
       </c>
       <c r="K76" t="str">
         <v>Valuation_AIC_ES_MCP</v>
@@ -3220,7 +3219,7 @@
         <v>1</v>
       </c>
       <c r="J80" t="str">
-        <v>1.02</v>
+        <v>1.00</v>
       </c>
       <c r="K80" t="str">
         <v>Delete_Portfolio_FR_MCP</v>
@@ -3255,7 +3254,7 @@
         <v>2</v>
       </c>
       <c r="J81" t="str">
-        <v>2.02</v>
+        <v>2.00</v>
       </c>
       <c r="K81" t="str">
         <v>Load_compare_MP_FR_MCP</v>
@@ -3290,7 +3289,7 @@
         <v>2</v>
       </c>
       <c r="J82" t="str">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="K82" t="str">
         <v>Load_compare_Spreads_FR_MCP</v>
@@ -3325,7 +3324,7 @@
         <v>4</v>
       </c>
       <c r="J83" t="str">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="K83" t="str">
         <v>Load_POS_FR_MCP</v>
@@ -3360,7 +3359,7 @@
         <v>7</v>
       </c>
       <c r="J84" t="str">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="K84" t="str">
         <v>Valuation_FR_MCP, Valuation_FR_MCP (SOT FX rerun), Valuation_FR_MCP Export Only requested by user</v>
@@ -3395,7 +3394,7 @@
         <v>4</v>
       </c>
       <c r="J85" t="str">
-        <v>6.77</v>
+        <v>6.75</v>
       </c>
       <c r="K85" t="str">
         <v>CSRBB_Valuation_FR_MCP, CSRBB_Valuation_Qtr_FR_MCP, CSRBB_Valuation_Qtr_FR_MCP rr</v>
@@ -3430,7 +3429,7 @@
         <v>5</v>
       </c>
       <c r="J86" t="str">
-        <v>8.31</v>
+        <v>8.29</v>
       </c>
       <c r="K86" t="str">
         <v>CSRBB_Planning_FR_MCP, CSRBB_Planning_Qtr_FR_MCP</v>
@@ -3465,7 +3464,7 @@
         <v>4</v>
       </c>
       <c r="J87" t="str">
-        <v>8.38</v>
+        <v>8.36</v>
       </c>
       <c r="K87" t="str">
         <v>EC_FR_MCP</v>
@@ -3500,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="J88" t="str">
-        <v>8.74</v>
+        <v>8.72</v>
       </c>
       <c r="K88" t="str">
         <v>GAP_FR_MCP, GAP_FR_MCP , GAP_FR_MCP rr print marker</v>
@@ -3535,7 +3534,7 @@
         <v>4</v>
       </c>
       <c r="J89" t="str">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="K89" t="str">
         <v>KR_FR_MCP</v>
@@ -3570,7 +3569,7 @@
         <v>1</v>
       </c>
       <c r="J90" t="str">
-        <v>10.12</v>
+        <v>10.10</v>
       </c>
       <c r="K90" t="str">
         <v>Import_Strategies_FR_MCP</v>
@@ -3605,7 +3604,7 @@
         <v>9</v>
       </c>
       <c r="J91" t="str">
-        <v>10.63</v>
+        <v>10.90</v>
       </c>
       <c r="K91" t="str">
         <v>Planning_FR_MCP, Planning_FR_MCP rr, Planning_FR_MCP rr2 (after manual QRM run for Run 1 INC14544643), Planning_FR_MCP rr2 (manual QRM run for Run 1 INC14544643), Planning_FR_MCP NII EXPORT</v>
@@ -3640,7 +3639,7 @@
         <v>3</v>
       </c>
       <c r="J92" t="str">
-        <v>11.14</v>
+        <v>11.11</v>
       </c>
       <c r="K92" t="str">
         <v>ITS_FR_MCP</v>
@@ -3675,7 +3674,7 @@
         <v>2</v>
       </c>
       <c r="J93" t="str">
-        <v>11.39</v>
+        <v>11.35</v>
       </c>
       <c r="K93" t="str">
         <v>Valuation_AIC_FR_MCP</v>
@@ -3780,7 +3779,7 @@
         <v>1</v>
       </c>
       <c r="J96" t="str">
-        <v>1.02</v>
+        <v>1.00</v>
       </c>
       <c r="K96" t="str">
         <v>Delete_Portfolio_IT_MCP, Delete_Portfolio_MCP</v>
@@ -3815,10 +3814,10 @@
         <v>2</v>
       </c>
       <c r="J97" t="str">
-        <v>2.02</v>
+        <v>2.00</v>
       </c>
       <c r="K97" t="str">
-        <v>Load_compare_MP_IT_MCP, Load_compare_MP_IT_MCP rr, Load_compare_MP_IT_MCP rr removed import workflow, Load_compare_MP_IT_MCP rr updated workflow path , Load_MP_MCP, Load_compare_MP_IT_MCP users signoff in PAPI</v>
+        <v>Load_compare_MP_IT_MCP, Load_compare_MP_IT_MCP rr, Load_compare_MP_IT_MCP rr removed import workflow, Load_compare_MP_IT_MCP rr updated workflow path, Load_MP_MCP, Load_compare_MP_IT_MCP users signoff in PAPI</v>
       </c>
     </row>
     <row r="98">
@@ -3850,7 +3849,7 @@
         <v>2</v>
       </c>
       <c r="J98" t="str">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="K98" t="str">
         <v>Load_compare_Spreads_IT_MCP, Load_compare_Spreads_IT_MCP rr, Load_Spreads_MCP</v>
@@ -3885,7 +3884,7 @@
         <v>5</v>
       </c>
       <c r="J99" t="str">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="K99" t="str">
         <v>Load_POS_IT_MCP, Load_POS_IT_MCP rr, Load_POS_IT_MCP rr mismatch in NTG file name, Load_POS_IT_MCP NTG load only, Load_POS_MCP, LOAD_POS_IT_MCP_VOS_UPGRADE, Load_POS_IT_MCP copydbruns</v>
@@ -3920,7 +3919,7 @@
         <v>10</v>
       </c>
       <c r="J100" t="str">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="K100" t="str">
         <v>Valuation_IT_MCP, Valuation_MCP, Valuation_MCP_Export</v>
@@ -3955,7 +3954,7 @@
         <v>4</v>
       </c>
       <c r="J101" t="str">
-        <v>6.77</v>
+        <v>6.75</v>
       </c>
       <c r="K101" t="str">
         <v>CSRBB_Valuation_IT_MCP, CSRBB_Valuation_Qtr_IT_MCP, CSRBB_Valuation_MCP, CSRBB_Valuation_Qtr_MCP</v>
@@ -3990,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="J102" t="str">
-        <v>8.31</v>
+        <v>8.29</v>
       </c>
       <c r="K102" t="str">
         <v>CSRBB_Planning_IT_MCP, CSRBB_Planning_Qtr_IT_MCP, CSRBB_Planning_IT_MCP (copy)</v>
@@ -4025,7 +4024,7 @@
         <v>4</v>
       </c>
       <c r="J103" t="str">
-        <v>8.38</v>
+        <v>8.36</v>
       </c>
       <c r="K103" t="str">
         <v>EC_IT_MCP, EC_MCP, EC_NPV_Export</v>
@@ -4060,7 +4059,7 @@
         <v>1</v>
       </c>
       <c r="J104" t="str">
-        <v>8.74</v>
+        <v>8.72</v>
       </c>
       <c r="K104" t="str">
         <v>GAP_IT_MCP, GAP_MCP, GAP_MCP IT Printmarkers</v>
@@ -4095,7 +4094,7 @@
         <v>5</v>
       </c>
       <c r="J105" t="str">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="K105" t="str">
         <v>KR_IT_MCP, KR_BPV_Export, KR_MCP</v>
@@ -4130,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="J106" t="str">
-        <v>10.12</v>
+        <v>10.10</v>
       </c>
       <c r="K106" t="str">
         <v>Import_Strategies_IT_MCP</v>
@@ -4165,7 +4164,7 @@
         <v>7</v>
       </c>
       <c r="J107" t="str">
-        <v>10.63</v>
+        <v>10.90</v>
       </c>
       <c r="K107" t="str">
         <v>Planning_IT_MCP, Planning_IT_MCP rr file in use</v>
@@ -4200,7 +4199,7 @@
         <v>2</v>
       </c>
       <c r="J108" t="str">
-        <v>11.14</v>
+        <v>11.11</v>
       </c>
       <c r="K108" t="str">
         <v>ITS_IT_MCP</v>
@@ -4235,7 +4234,7 @@
         <v>2</v>
       </c>
       <c r="J109" t="str">
-        <v>11.39</v>
+        <v>11.35</v>
       </c>
       <c r="K109" t="str">
         <v>Valuation_AIC_IT_MCP, Valuation_AIC_IT_MCP rr, Valuation_AIC_MCP</v>
@@ -4375,7 +4374,7 @@
         <v>1</v>
       </c>
       <c r="J113" t="str">
-        <v>1.02</v>
+        <v>1.00</v>
       </c>
       <c r="K113" t="str">
         <v>Delete_Portfolio_LU_MCP, Delete_Portfolio_MCP</v>
@@ -4410,7 +4409,7 @@
         <v>2</v>
       </c>
       <c r="J114" t="str">
-        <v>2.02</v>
+        <v>2.00</v>
       </c>
       <c r="K114" t="str">
         <v>Load_compare_MP_LU_MCP, Load_compare_MP_LU_MCP rr, Load_MP_MCP</v>
@@ -4445,7 +4444,7 @@
         <v>2</v>
       </c>
       <c r="J115" t="str">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="K115" t="str">
         <v>Load_compare_Spreads_LU_MCP, Load_compare_Spreads_LU_MCP rr, Load_Spreads_MCP</v>
@@ -4480,7 +4479,7 @@
         <v>7</v>
       </c>
       <c r="J116" t="str">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="K116" t="str">
         <v>Load_POS_LU_MCP, Load_POS_MCP, POS_MCP_Export, Load_POS_LU_MCP rr INC14698835</v>
@@ -4515,7 +4514,7 @@
         <v>8</v>
       </c>
       <c r="J117" t="str">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="K117" t="str">
         <v>Valuation_LU_MCP, Valuation_LU_MCP (SOT FX rerun), Valuation_MCP, Valuation_MCP_Export, Valuation_MCP_Export valshock</v>
@@ -4550,7 +4549,7 @@
         <v>4</v>
       </c>
       <c r="J118" t="str">
-        <v>6.77</v>
+        <v>6.75</v>
       </c>
       <c r="K118" t="str">
         <v>CSRBB_Valuation_LU_MCP, CSRBB_Valuation_Qtr_LU_MCP, CSRBB_Valuation_MCP</v>
@@ -4585,7 +4584,7 @@
         <v>4</v>
       </c>
       <c r="J119" t="str">
-        <v>8.31</v>
+        <v>8.29</v>
       </c>
       <c r="K119" t="str">
         <v>CSRBB_Planning_LU_MCP, CSRBB_Planning_Qtr_LU_MCP, CSRBB_Planning_LU_MCP rr, CSRBB_Planning_LU_MCP rr2, CSRBB_Planning_MCP</v>
@@ -4620,7 +4619,7 @@
         <v>5</v>
       </c>
       <c r="J120" t="str">
-        <v>8.38</v>
+        <v>8.36</v>
       </c>
       <c r="K120" t="str">
         <v>EC_LU_MCP, EC_MCP, EC_NPV_Export, EC_NPV_Export rr</v>
@@ -4655,7 +4654,7 @@
         <v>1</v>
       </c>
       <c r="J121" t="str">
-        <v>8.74</v>
+        <v>8.72</v>
       </c>
       <c r="K121" t="str">
         <v>GAP_LU_MCP, GAP_MCP, GAP_LU_MCP rr, GAP_LU_MCP rr3</v>
@@ -4690,7 +4689,7 @@
         <v>4</v>
       </c>
       <c r="J122" t="str">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="K122" t="str">
         <v>KR_LU_MCP, KR_BPV_Export, KR_BPV_Export valshock, KR_MCP</v>
@@ -4725,7 +4724,7 @@
         <v>3</v>
       </c>
       <c r="J123" t="str">
-        <v>10.12</v>
+        <v>10.10</v>
       </c>
       <c r="K123" t="str">
         <v>Import_Strategies_LU_MCP, Import_Strategies_IG_MCP, Import_Strategies_Risk_MCP</v>
@@ -4760,7 +4759,7 @@
         <v>10</v>
       </c>
       <c r="J124" t="str">
-        <v>10.63</v>
+        <v>10.90</v>
       </c>
       <c r="K124" t="str">
         <v>Planning_LU_MCP, Planning_MCP, Planning_MCP_Export</v>
@@ -4795,7 +4794,7 @@
         <v>2</v>
       </c>
       <c r="J125" t="str">
-        <v>11.39</v>
+        <v>11.35</v>
       </c>
       <c r="K125" t="str">
         <v>Valuation_AIC_LU_MCP, Valuation_AIC_MCP</v>
@@ -4935,7 +4934,7 @@
         <v>8</v>
       </c>
       <c r="J129" t="str">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="K129" t="str">
         <v>Load_POS_NLBTR_MCP</v>
@@ -4970,7 +4969,7 @@
         <v>7</v>
       </c>
       <c r="J130" t="str">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="K130" t="str">
         <v>Valuation_NLBTR_MCP</v>
@@ -5005,7 +5004,7 @@
         <v>5</v>
       </c>
       <c r="J131" t="str">
-        <v>6.77</v>
+        <v>6.75</v>
       </c>
       <c r="K131" t="str">
         <v>CSRBB_Valuation_NLBTR_MCP, CSRBB_Valuation_NLBTR_MCP rr, CSRBB_Valuation_Qtr_NLBTR_MCP, CSRBB_Valuation_Qtr_NLBTR_MCP (rr), CSRBB_Valuation_Qtr_NLBTR_MCP rr (resume after send mail failure)</v>
@@ -5040,7 +5039,7 @@
         <v>6</v>
       </c>
       <c r="J132" t="str">
-        <v>8.31</v>
+        <v>8.29</v>
       </c>
       <c r="K132" t="str">
         <v>CSRBB_Planning_NLBTR_MCP, CSRBB_Planning_NLBTR_MCP (run from line 42 down), CSRBB_Planning_NLBTR_MCP (run up to line 38 set defaults), CSRBB_Planning_NLBTR_MCP rr, CSRBB_Planning_Qtr_NLBTR_MCP, CSRBB_Planning_Qtr_NLBTR_MCP (rr), CSRBB_Planning_NLBTR_MCP rr creation of uncorrupted strategy, CSRBB_Planning_NLBTR_MCP rr from line 42 down, CSRBB_Planning_NLBTR_MCP rr2</v>
@@ -5075,7 +5074,7 @@
         <v>5</v>
       </c>
       <c r="J133" t="str">
-        <v>8.38</v>
+        <v>8.36</v>
       </c>
       <c r="K133" t="str">
         <v>EC_NLBTR_MCP</v>
@@ -5110,7 +5109,7 @@
         <v>1</v>
       </c>
       <c r="J134" t="str">
-        <v>8.74</v>
+        <v>8.72</v>
       </c>
       <c r="K134" t="str">
         <v>GAP_NLBTR_MCP, GAP_NLBTR_MCP rr, GAP_NLBTR_MCP rr (Export)</v>
@@ -5145,7 +5144,7 @@
         <v>5</v>
       </c>
       <c r="J135" t="str">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="K135" t="str">
         <v>KR_NLBTR_MCP</v>
@@ -5180,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="J136" t="str">
-        <v>10.12</v>
+        <v>10.10</v>
       </c>
       <c r="K136" t="str">
         <v>Import_Strategies_NLBTR_MCP, Import_Strategies_NLBTR_MCP_2, Import_Strategies_NLBTR_MCP_2 (test), Import_Strategies_NLBTR_MCP_2 rr (post test), Import_Strategies_NLBTR_MCP_2 rr (strat 1 corrected try 2), Import_Strategies_NLBTR_MCP_2 rr (strat 1 corrected)</v>
@@ -5215,7 +5214,7 @@
         <v>10</v>
       </c>
       <c r="J137" t="str">
-        <v>10.63</v>
+        <v>10.90</v>
       </c>
       <c r="K137" t="str">
         <v>Planning_NLBTR_MCP, Planning_NLBTR_MCP_2, Planning_NLBTR_MCP_2 (rr export only WF update untick remove unn data), Planning_NLBTR_MCP_2 (rr from line 72 down), Planning_NLBTR_MCP_2 (rr2 INC14346514 memory issue), Planning_NLBTR_MCP_2 (rr2 export only WF update untick remove unn data), Planning_NLBTR_MCP_2 (rr3 export only WF update untick remove unn data), Planning_NLBTR_MCP_2 (rr4 split reports + export only WF update untick remove unn data), Planning_NLBTR_MCP_2 rr (MDL), Planning_NLBTR_MCP_2 rr IN14692534, Planning_NLBTR_MCP_2 rr (strat 1 corrected try2), Planning_NLBTR_MCP_2 rr (strat 1 corrected)</v>
@@ -5250,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="J138" t="str">
-        <v>11.14</v>
+        <v>11.11</v>
       </c>
       <c r="K138" t="str">
         <v>ITS_NLBTR_MCP</v>
@@ -5320,7 +5319,7 @@
         <v>1</v>
       </c>
       <c r="J140" t="str">
-        <v>1.02</v>
+        <v>1.00</v>
       </c>
       <c r="K140" t="str">
         <v>Delete_Portfolio_NL_MCP</v>
@@ -5355,7 +5354,7 @@
         <v>2</v>
       </c>
       <c r="J141" t="str">
-        <v>2.02</v>
+        <v>2.00</v>
       </c>
       <c r="K141" t="str">
         <v>Load_compare_MP_NL_MCP, Load_compare_MP_NL_MCP_2601, Load_compare_MP_NL_MCP_2601_1</v>
@@ -5390,7 +5389,7 @@
         <v>2</v>
       </c>
       <c r="J142" t="str">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="K142" t="str">
         <v>Load_compare_Spreads_NL_MCP</v>
@@ -5425,7 +5424,7 @@
         <v>3</v>
       </c>
       <c r="J143" t="str">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="K143" t="str">
         <v>Load_POS_NL_MCP</v>
@@ -5460,7 +5459,7 @@
         <v>6</v>
       </c>
       <c r="J144" t="str">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="K144" t="str">
         <v>Valuation_NL_MCP</v>
@@ -5565,7 +5564,7 @@
         <v>5</v>
       </c>
       <c r="J147" t="str">
-        <v>8.38</v>
+        <v>8.36</v>
       </c>
       <c r="K147" t="str">
         <v>EC_NL_MCP, EC_NL_MCP rerun after stuck run</v>
@@ -5600,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="J148" t="str">
-        <v>8.74</v>
+        <v>8.72</v>
       </c>
       <c r="K148" t="str">
         <v>GAP_NL_MCP</v>
@@ -5635,7 +5634,7 @@
         <v>4</v>
       </c>
       <c r="J149" t="str">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="K149" t="str">
         <v>KR_NL_MCP, KR_NL_MCP , KR_NL_MCP rr workaround</v>
@@ -5670,7 +5669,7 @@
         <v>1</v>
       </c>
       <c r="J150" t="str">
-        <v>10.12</v>
+        <v>10.10</v>
       </c>
       <c r="K150" t="str">
         <v>Import_Strategies_NL_MCP, Import_Strategies_NL_MCP Feb26 rerun</v>
@@ -5705,7 +5704,7 @@
         <v>4</v>
       </c>
       <c r="J151" t="str">
-        <v>10.63</v>
+        <v>10.90</v>
       </c>
       <c r="K151" t="str">
         <v>Combined_Planning_NL_MCP, Combined_Planning_NL_MCP Feb26 rerun, Combined_Planning_NL_MCP rr w/ updated strategies</v>
@@ -5740,7 +5739,7 @@
         <v>3</v>
       </c>
       <c r="J152" t="str">
-        <v>11.14</v>
+        <v>11.11</v>
       </c>
       <c r="K152" t="str">
         <v>ITS_NL_MCP</v>
@@ -5775,7 +5774,7 @@
         <v>2</v>
       </c>
       <c r="J153" t="str">
-        <v>11.39</v>
+        <v>11.35</v>
       </c>
       <c r="K153" t="str">
         <v>Valuation_AIC_NL_MCP</v>
@@ -5950,7 +5949,7 @@
         <v>1</v>
       </c>
       <c r="J158" t="str">
-        <v>1.02</v>
+        <v>1.00</v>
       </c>
       <c r="K158" t="str">
         <v>Delete_Portfolio_PL_MCP, Delete_Portfolio_MCP</v>
@@ -5985,7 +5984,7 @@
         <v>2</v>
       </c>
       <c r="J159" t="str">
-        <v>2.02</v>
+        <v>2.00</v>
       </c>
       <c r="K159" t="str">
         <v>Load_compare_MP_PL_MCP (copy), Load_compare_MP_PL_MCP, Load_compare_MP_PL_MCP ESM0548459, Load_MP_MCP, Load_MP_MCP RR</v>
@@ -6020,7 +6019,7 @@
         <v>2</v>
       </c>
       <c r="J160" t="str">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="K160" t="str">
         <v>Load_compare_Spreads_PL_MCP, Load_Spreads_MCP</v>
@@ -6055,7 +6054,7 @@
         <v>6</v>
       </c>
       <c r="J161" t="str">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="K161" t="str">
         <v>Load_POS_PL_MCP, Load_POS_MCP, POS_MCP_Export</v>
@@ -6090,10 +6089,10 @@
         <v>10</v>
       </c>
       <c r="J162" t="str">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="K162" t="str">
-        <v>Valuation_PL_MCP, Valuation_RegQ_PL_MCP, Valuation_PL_MCP ESM0548459 , Valuation_MCP, Valuation_MCP PL RR, Valuation_MCP_Export, Valuation_MCP_Export NPV reports, Valuation_MCP_Export PL rr</v>
+        <v>Valuation_PL_MCP, Valuation_RegQ_PL_MCP, Valuation_PL_MCP ESM0548459, Valuation_MCP, Valuation_MCP PL RR, Valuation_MCP_Export, Valuation_MCP_Export NPV reports, Valuation_MCP_Export PL rr</v>
       </c>
     </row>
     <row r="163">
@@ -6125,7 +6124,7 @@
         <v>3</v>
       </c>
       <c r="J163" t="str">
-        <v>6.77</v>
+        <v>6.75</v>
       </c>
       <c r="K163" t="str">
         <v>CSRBB_Valuation_PL_MCP, CSRBB_Valuation_Qtr_PL_MCP, CSRBB_Valuation_MCP</v>
@@ -6160,7 +6159,7 @@
         <v>4</v>
       </c>
       <c r="J164" t="str">
-        <v>8.31</v>
+        <v>8.29</v>
       </c>
       <c r="K164" t="str">
         <v>CSRBB_Planning_PL_MCP, CSRBB_Planning_Qtr_PL_MCP, CSRBB_Planning_MCP rr, CSRBB_Planning_PL_MCP RR3, CSRBB_Planning_MCP</v>
@@ -6195,10 +6194,10 @@
         <v>5</v>
       </c>
       <c r="J165" t="str">
-        <v>8.38</v>
+        <v>8.36</v>
       </c>
       <c r="K165" t="str">
-        <v>EC_PL_MCP, EC_PL_MCP ESM0548459 , EC_MCP, EC_NPV_Export, EC_NPV_Export NPV PL</v>
+        <v>EC_PL_MCP, EC_PL_MCP ESM0548459, EC_MCP, EC_NPV_Export, EC_NPV_Export NPV PL</v>
       </c>
     </row>
     <row r="166">
@@ -6230,7 +6229,7 @@
         <v>2</v>
       </c>
       <c r="J166" t="str">
-        <v>8.74</v>
+        <v>8.72</v>
       </c>
       <c r="K166" t="str">
         <v xml:space="preserve">GAP_PL_MCP, GAP_PL_MCP rr due to Q3 stopped working (INC14536561), GAP_MCP, GAP_PL_MCP LAD_SF only, GAP_PL_MCP LAD_SF only </v>
@@ -6265,7 +6264,7 @@
         <v>4</v>
       </c>
       <c r="J167" t="str">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="K167" t="str">
         <v>KR_PL_MCP, KR_BPV_Export, KR_BPV_Export NPV PL , KR_MCP</v>
@@ -6300,7 +6299,7 @@
         <v>1</v>
       </c>
       <c r="J168" t="str">
-        <v>10.12</v>
+        <v>10.10</v>
       </c>
       <c r="K168" t="str">
         <v>Import_Strategies_PL_MCP, Import_Strategies_PL_MCP ESM0549311</v>
@@ -6335,7 +6334,7 @@
         <v>13</v>
       </c>
       <c r="J169" t="str">
-        <v>10.63</v>
+        <v>10.90</v>
       </c>
       <c r="K169" t="str">
         <v>Planning_PL_MCP MDS, Planning_PL_MCP Run1, Planning_PL_MCP Run2, Planning_PL_MCP Run3, Planning_PL_MCP S118, Planning_RSS_PL_MCP, Planning_RSS_PL_MCP Fordet, Planning_RSS_PL_MCP Rerun, Planning_RSS_PL_MCP rr IG onwards, Planning_PL_MCP, Planning_PL_MCP ESM0549311, Planning_PL_MCP rr post aftercare, Planning_MCP, Planning_MCP_Export</v>
@@ -6370,7 +6369,7 @@
         <v>3</v>
       </c>
       <c r="J170" t="str">
-        <v>11.14</v>
+        <v>11.11</v>
       </c>
       <c r="K170" t="str">
         <v>ITS_PL_MCP, ITS_MCP</v>
@@ -6405,7 +6404,7 @@
         <v>2</v>
       </c>
       <c r="J171" t="str">
-        <v>11.39</v>
+        <v>11.35</v>
       </c>
       <c r="K171" t="str">
         <v>Valuation_AIC_PL_MCP, Valuation_AIC_MCP</v>
@@ -6650,7 +6649,7 @@
         <v>1</v>
       </c>
       <c r="J178" t="str">
-        <v>1.02</v>
+        <v>1.00</v>
       </c>
       <c r="K178" t="str">
         <v>Delete_Portfolio_RO_MCP</v>
@@ -6685,7 +6684,7 @@
         <v>2</v>
       </c>
       <c r="J179" t="str">
-        <v>2.02</v>
+        <v>2.00</v>
       </c>
       <c r="K179" t="str">
         <v>Load_compare_MP_RO_MCP</v>
@@ -6720,7 +6719,7 @@
         <v>2</v>
       </c>
       <c r="J180" t="str">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="K180" t="str">
         <v>Load_compare_Spreads_RO_MCP</v>
@@ -6755,7 +6754,7 @@
         <v>3</v>
       </c>
       <c r="J181" t="str">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="K181" t="str">
         <v>Load_POS_RO_MCP, Load_POS_RO_MCP (copy)</v>
@@ -6790,7 +6789,7 @@
         <v>4</v>
       </c>
       <c r="J182" t="str">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="K182" t="str">
         <v>Valuation_RO_MCP</v>
@@ -6825,7 +6824,7 @@
         <v>3</v>
       </c>
       <c r="J183" t="str">
-        <v>6.77</v>
+        <v>6.75</v>
       </c>
       <c r="K183" t="str">
         <v>CSRBB_Valuation_RO_MCP</v>
@@ -6860,7 +6859,7 @@
         <v>4</v>
       </c>
       <c r="J184" t="str">
-        <v>8.31</v>
+        <v>8.29</v>
       </c>
       <c r="K184" t="str">
         <v>CSRBB_Planning_RO_MCP</v>
@@ -6895,7 +6894,7 @@
         <v>4</v>
       </c>
       <c r="J185" t="str">
-        <v>8.38</v>
+        <v>8.36</v>
       </c>
       <c r="K185" t="str">
         <v>EC_RO_MCP, EC_RO_MCP _incorrect EC WF</v>
@@ -6930,7 +6929,7 @@
         <v>4</v>
       </c>
       <c r="J186" t="str">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="K186" t="str">
         <v>KR_RO_MCP</v>
@@ -6965,7 +6964,7 @@
         <v>1</v>
       </c>
       <c r="J187" t="str">
-        <v>10.12</v>
+        <v>10.10</v>
       </c>
       <c r="K187" t="str">
         <v>Import_Strategies_RO_MCP</v>
@@ -7000,7 +6999,7 @@
         <v>6</v>
       </c>
       <c r="J188" t="str">
-        <v>10.63</v>
+        <v>10.90</v>
       </c>
       <c r="K188" t="str">
         <v>Planning_RO_MCP</v>
@@ -7035,7 +7034,7 @@
         <v>3</v>
       </c>
       <c r="J189" t="str">
-        <v>11.14</v>
+        <v>11.11</v>
       </c>
       <c r="K189" t="str">
         <v>ITS_RO_MCP</v>
@@ -7105,7 +7104,7 @@
         <v>1</v>
       </c>
       <c r="J191" t="str">
-        <v>1.02</v>
+        <v>1.00</v>
       </c>
       <c r="K191" t="str">
         <v>Delete_Portfolio_TR_MCP</v>
@@ -7140,7 +7139,7 @@
         <v>2</v>
       </c>
       <c r="J192" t="str">
-        <v>2.02</v>
+        <v>2.00</v>
       </c>
       <c r="K192" t="str">
         <v>Load_compare_MP_TR_MCP, Load_compare_MP_TR_MCP (copy)</v>
@@ -7210,7 +7209,7 @@
         <v>2</v>
       </c>
       <c r="J194" t="str">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="K194" t="str">
         <v>Load_compare_Spreads_TR_MCP</v>
@@ -7245,7 +7244,7 @@
         <v>4</v>
       </c>
       <c r="J195" t="str">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="K195" t="str">
         <v>Load_POS_TR_MCP</v>
@@ -7280,7 +7279,7 @@
         <v>7</v>
       </c>
       <c r="J196" t="str">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="K196" t="str">
         <v>Valuation_TR_MCP, Valuation_TR_MCP (SOT FX rerun), Valuation_TR_MCP INC14517289, Valuation_TR_MCP files missing in the folder, Valuation_TR_MCP rr, Valuation_TR_MCP (copy)</v>
@@ -7315,7 +7314,7 @@
         <v>4</v>
       </c>
       <c r="J197" t="str">
-        <v>6.77</v>
+        <v>6.75</v>
       </c>
       <c r="K197" t="str">
         <v>CSRBB_Valuation_Qtr_TR_MCP, CSRBB_Valuation_TR_MCP</v>
@@ -7350,7 +7349,7 @@
         <v>5</v>
       </c>
       <c r="J198" t="str">
-        <v>8.31</v>
+        <v>8.29</v>
       </c>
       <c r="K198" t="str">
         <v>CSRBB_Planning_Qtr_TR_MCP, CSRBB_Planning_TR_MCP</v>
@@ -7385,7 +7384,7 @@
         <v>4</v>
       </c>
       <c r="J199" t="str">
-        <v>8.38</v>
+        <v>8.36</v>
       </c>
       <c r="K199" t="str">
         <v>EC_TR_MCP, EC_TR_MCP_incorrect EC WF</v>
@@ -7420,7 +7419,7 @@
         <v>1</v>
       </c>
       <c r="J200" t="str">
-        <v>8.74</v>
+        <v>8.72</v>
       </c>
       <c r="K200" t="str">
         <v>GAP_TR_MCP</v>
@@ -7455,7 +7454,7 @@
         <v>4</v>
       </c>
       <c r="J201" t="str">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="K201" t="str">
         <v>KR_TR_MCP</v>
@@ -7490,7 +7489,7 @@
         <v>1</v>
       </c>
       <c r="J202" t="str">
-        <v>10.12</v>
+        <v>10.10</v>
       </c>
       <c r="K202" t="str">
         <v>Import_Strategies_TR_MCP</v>
@@ -7525,7 +7524,7 @@
         <v>7</v>
       </c>
       <c r="J203" t="str">
-        <v>10.63</v>
+        <v>10.90</v>
       </c>
       <c r="K203" t="str">
         <v>Planning_TR_MCP</v>
@@ -7560,7 +7559,7 @@
         <v>3</v>
       </c>
       <c r="J204" t="str">
-        <v>11.14</v>
+        <v>11.11</v>
       </c>
       <c r="K204" t="str">
         <v>ITS_TR_MCP</v>
@@ -7595,7 +7594,7 @@
         <v>3</v>
       </c>
       <c r="J205" t="str">
-        <v>11.39</v>
+        <v>11.35</v>
       </c>
       <c r="K205" t="str">
         <v>Valuation_AIC_TR_MCP</v>
@@ -7735,7 +7734,7 @@
         <v>1</v>
       </c>
       <c r="J209" t="str">
-        <v>1.02</v>
+        <v>1.00</v>
       </c>
       <c r="K209" t="str">
         <v>Delete_Portfolio_US_MCP</v>
@@ -7770,7 +7769,7 @@
         <v>2</v>
       </c>
       <c r="J210" t="str">
-        <v>2.02</v>
+        <v>2.00</v>
       </c>
       <c r="K210" t="str">
         <v>Load_compare_MP_US_MCP</v>
@@ -7805,7 +7804,7 @@
         <v>2</v>
       </c>
       <c r="J211" t="str">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="K211" t="str">
         <v>Load_compare_Spreads_US_MCP</v>
@@ -7840,7 +7839,7 @@
         <v>3</v>
       </c>
       <c r="J212" t="str">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="K212" t="str">
         <v>Load_POS_US_MCP</v>
@@ -7875,7 +7874,7 @@
         <v>5</v>
       </c>
       <c r="J213" t="str">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="K213" t="str">
         <v>Valuation_US_MCP</v>
@@ -7910,7 +7909,7 @@
         <v>2</v>
       </c>
       <c r="J214" t="str">
-        <v>6.77</v>
+        <v>6.75</v>
       </c>
       <c r="K214" t="str">
         <v>CSRBB_Valuation_Qtr_US_MCP, CSRBB_Valuation_US_MCP</v>
@@ -7945,7 +7944,7 @@
         <v>4</v>
       </c>
       <c r="J215" t="str">
-        <v>8.31</v>
+        <v>8.29</v>
       </c>
       <c r="K215" t="str">
         <v>CSRBB_Planning_Qtr_US_MCP, CSRBB_Planning_US_MCP</v>
@@ -7980,7 +7979,7 @@
         <v>1</v>
       </c>
       <c r="J216" t="str">
-        <v>8.74</v>
+        <v>8.72</v>
       </c>
       <c r="K216" t="str">
         <v>GAP_US_MCP, GAP_US_MCP rr</v>
@@ -8015,7 +8014,7 @@
         <v>4</v>
       </c>
       <c r="J217" t="str">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="K217" t="str">
         <v>KR_US_MCP</v>
@@ -8050,7 +8049,7 @@
         <v>1</v>
       </c>
       <c r="J218" t="str">
-        <v>10.12</v>
+        <v>10.10</v>
       </c>
       <c r="K218" t="str">
         <v>Import_Strategies_US_MCP</v>
@@ -8085,7 +8084,7 @@
         <v>5</v>
       </c>
       <c r="J219" t="str">
-        <v>10.63</v>
+        <v>10.90</v>
       </c>
       <c r="K219" t="str">
         <v>Planning_US_MCP</v>
@@ -8120,7 +8119,7 @@
         <v>3</v>
       </c>
       <c r="J220" t="str">
-        <v>11.14</v>
+        <v>11.11</v>
       </c>
       <c r="K220" t="str">
         <v>ITS_US_MCP</v>
@@ -8155,7 +8154,7 @@
         <v>2</v>
       </c>
       <c r="J221" t="str">
-        <v>11.39</v>
+        <v>11.35</v>
       </c>
       <c r="K221" t="str">
         <v>Valuation_AIC_US_MCP</v>
@@ -8273,7 +8272,7 @@
         <v>12</v>
       </c>
       <c r="H2" t="str">
-        <v>1.02</v>
+        <v>1.00</v>
       </c>
       <c r="I2">
         <v>46</v>
@@ -8302,7 +8301,7 @@
         <v>12</v>
       </c>
       <c r="H3" t="str">
-        <v>2.02</v>
+        <v>2.00</v>
       </c>
       <c r="I3">
         <v>46</v>
@@ -8360,7 +8359,7 @@
         <v>12</v>
       </c>
       <c r="H5" t="str">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="I5">
         <v>46</v>
@@ -8389,7 +8388,7 @@
         <v>15</v>
       </c>
       <c r="H6" t="str">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="I6">
         <v>57</v>
@@ -8447,7 +8446,7 @@
         <v>15</v>
       </c>
       <c r="H8" t="str">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="I8">
         <v>56</v>
@@ -8505,7 +8504,7 @@
         <v>12</v>
       </c>
       <c r="H10" t="str">
-        <v>6.77</v>
+        <v>6.75</v>
       </c>
       <c r="I10">
         <v>44</v>
@@ -8563,7 +8562,7 @@
         <v>12</v>
       </c>
       <c r="H12" t="str">
-        <v>8.31</v>
+        <v>8.29</v>
       </c>
       <c r="I12">
         <v>42</v>
@@ -8592,7 +8591,7 @@
         <v>13</v>
       </c>
       <c r="H13" t="str">
-        <v>8.38</v>
+        <v>8.36</v>
       </c>
       <c r="I13">
         <v>47</v>
@@ -8621,7 +8620,7 @@
         <v>13</v>
       </c>
       <c r="H14" t="str">
-        <v>8.74</v>
+        <v>8.72</v>
       </c>
       <c r="I14">
         <v>46</v>
@@ -8650,7 +8649,7 @@
         <v>14</v>
       </c>
       <c r="H15" t="str">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="I15">
         <v>51</v>
@@ -8679,7 +8678,7 @@
         <v>15</v>
       </c>
       <c r="H16" t="str">
-        <v>10.12</v>
+        <v>10.10</v>
       </c>
       <c r="I16">
         <v>49</v>
@@ -8708,7 +8707,7 @@
         <v>15</v>
       </c>
       <c r="H17" t="str">
-        <v>10.63</v>
+        <v>10.90</v>
       </c>
       <c r="I17">
         <v>49</v>
@@ -8737,7 +8736,7 @@
         <v>12</v>
       </c>
       <c r="H18" t="str">
-        <v>11.14</v>
+        <v>11.11</v>
       </c>
       <c r="I18">
         <v>37</v>
@@ -8766,7 +8765,7 @@
         <v>11</v>
       </c>
       <c r="H19" t="str">
-        <v>11.39</v>
+        <v>11.35</v>
       </c>
       <c r="I19">
         <v>31</v>
@@ -18411,7 +18410,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -19111,19 +19110,19 @@
         <v>ICDB</v>
       </c>
       <c r="B35" t="str">
-        <v>ac</v>
+        <v/>
       </c>
       <c r="C35" t="str">
         <v>Single-step adhoc</v>
       </c>
       <c r="D35" t="str">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>Super Light Maintenance</v>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -19131,19 +19130,19 @@
         <v>ICDB</v>
       </c>
       <c r="B36" t="str">
-        <v>CSRBB_Planning_Qtr_IRRBBCORE_MCP</v>
+        <v>ac</v>
       </c>
       <c r="C36" t="str">
         <v>Single-step adhoc</v>
       </c>
       <c r="D36" t="str">
-        <v>2512</v>
+        <v>2602</v>
       </c>
       <c r="E36">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>CSRBB quarterly Planning | NLWB_Lending | Live on ALM Core | CSRBB quarterly Planning | London | Live on ALM Core | CSRBB quarterly Planning | Singapore | Live on ALM Core | CSRBB quarterly Planning | Hong_Kong | Live on ALM Core | CSRBB quarterly Planning | Sofia | Live on ALM Core...</v>
+        <v>Super Light Maintenance</v>
       </c>
     </row>
     <row r="37">
@@ -19151,7 +19150,7 @@
         <v>ICDB</v>
       </c>
       <c r="B37" t="str">
-        <v>CSRBB_Planning_Qtr_IRRBBCORE_MCP rr due to the general rerun</v>
+        <v>CSRBB_Planning_Qtr_IRRBBCORE_MCP</v>
       </c>
       <c r="C37" t="str">
         <v>Single-step adhoc</v>
@@ -19160,10 +19159,10 @@
         <v>2512</v>
       </c>
       <c r="E37">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F37" t="str">
-        <v>CSRBB quarterly Planning | Singapore | Live on ALM Core | CSRBB quarterly Planning | Hong_Kong | Live on ALM Core | CSRBB quarterly Planning | Sofia | Live on ALM Core | Light Maintenance | CSRBB quarterly Planning | Prague | Live on ALM Core</v>
+        <v>CSRBB quarterly Planning | NLWB_Lending | Live on ALM Core | CSRBB quarterly Planning | London | Live on ALM Core | CSRBB quarterly Planning | Singapore | Live on ALM Core | CSRBB quarterly Planning | Hong_Kong | Live on ALM Core | CSRBB quarterly Planning | Sofia | Live on ALM Core...</v>
       </c>
     </row>
     <row r="38">
@@ -19171,7 +19170,7 @@
         <v>ICDB</v>
       </c>
       <c r="B38" t="str">
-        <v xml:space="preserve">CSRBB_Planning_Qtr_IRRBBCORE_sideloads_MCP 2025Q4 </v>
+        <v>CSRBB_Planning_Qtr_IRRBBCORE_MCP rr due to the general rerun</v>
       </c>
       <c r="C38" t="str">
         <v>Single-step adhoc</v>
@@ -19180,10 +19179,10 @@
         <v>2512</v>
       </c>
       <c r="E38">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F38" t="str">
-        <v>CSRBB quarterly Planning | London_CSRBB | Live on ALM Core | CSRBB quarterly Planning | Singapore_CSRBB | Live on ALM Core | CSRBB quarterly Planning | Shanghai_CSRBB | Live on ALM Core | CSRBB quarterly Planning | Tokyo_CSRBB | Live on ALM Core | Light Maintenance...</v>
+        <v>CSRBB quarterly Planning | Singapore | Live on ALM Core | CSRBB quarterly Planning | Hong_Kong | Live on ALM Core | CSRBB quarterly Planning | Sofia | Live on ALM Core | Light Maintenance | CSRBB quarterly Planning | Prague | Live on ALM Core</v>
       </c>
     </row>
     <row r="39">
@@ -19191,7 +19190,7 @@
         <v>ICDB</v>
       </c>
       <c r="B39" t="str">
-        <v>CSRBB_Valuation_Qtr_IRRBBCORE_MCP</v>
+        <v xml:space="preserve">CSRBB_Planning_Qtr_IRRBBCORE_sideloads_MCP 2025Q4 </v>
       </c>
       <c r="C39" t="str">
         <v>Single-step adhoc</v>
@@ -19200,10 +19199,10 @@
         <v>2512</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F39" t="str">
-        <v>CSRBB quarterly Valuation | NLWB_Lending | Live on ALM Core</v>
+        <v>CSRBB quarterly Planning | London_CSRBB | Live on ALM Core | CSRBB quarterly Planning | Singapore_CSRBB | Live on ALM Core | CSRBB quarterly Planning | Shanghai_CSRBB | Live on ALM Core | CSRBB quarterly Planning | Tokyo_CSRBB | Live on ALM Core | Light Maintenance...</v>
       </c>
     </row>
     <row r="40">
@@ -19211,7 +19210,7 @@
         <v>ICDB</v>
       </c>
       <c r="B40" t="str">
-        <v>CSRBB_Valuation_Qtr_IRRBBCORE_MCP rr</v>
+        <v>CSRBB_Valuation_Qtr_IRRBBCORE_MCP</v>
       </c>
       <c r="C40" t="str">
         <v>Single-step adhoc</v>
@@ -19220,10 +19219,10 @@
         <v>2512</v>
       </c>
       <c r="E40">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>CSRBB quarterly Valuation | NLWB_Lending | Live on ALM Core | CSRBB quarterly Valuation | London | Live on ALM Core | Light Maintenance | CSRBB quarterly Valuation | Singapore | Live on ALM Core | CSRBB quarterly Valuation | Hong_Kong | Live on ALM Core...</v>
+        <v>CSRBB quarterly Valuation | NLWB_Lending | Live on ALM Core</v>
       </c>
     </row>
     <row r="41">
@@ -19231,7 +19230,7 @@
         <v>ICDB</v>
       </c>
       <c r="B41" t="str">
-        <v>CSRBB_Valuation_Qtr_IRRBBCORE_MCP rr 2 due to the general rerun</v>
+        <v>CSRBB_Valuation_Qtr_IRRBBCORE_MCP rr</v>
       </c>
       <c r="C41" t="str">
         <v>Single-step adhoc</v>
@@ -19240,10 +19239,10 @@
         <v>2512</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F41" t="str">
-        <v>Light Maintenance | CSRBB quarterly Valuation | Singapore | Live on ALM Core | CSRBB quarterly Valuation | Hong_Kong | Live on ALM Core | CSRBB quarterly Valuation | Sofia | Live on ALM Core | CSRBB quarterly Valuation | Prague | Live on ALM Core</v>
+        <v>CSRBB quarterly Valuation | NLWB_Lending | Live on ALM Core | CSRBB quarterly Valuation | London | Live on ALM Core | Light Maintenance | CSRBB quarterly Valuation | Singapore | Live on ALM Core | CSRBB quarterly Valuation | Hong_Kong | Live on ALM Core...</v>
       </c>
     </row>
     <row r="42">
@@ -19251,7 +19250,7 @@
         <v>ICDB</v>
       </c>
       <c r="B42" t="str">
-        <v>CSRBB_Valuation_Qtr_IRRBBCORE_sideloads_MCP 2025Q4</v>
+        <v>CSRBB_Valuation_Qtr_IRRBBCORE_MCP rr 2 due to the general rerun</v>
       </c>
       <c r="C42" t="str">
         <v>Single-step adhoc</v>
@@ -19260,10 +19259,10 @@
         <v>2512</v>
       </c>
       <c r="E42">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F42" t="str">
-        <v>CSRBB quarterly Valuation | London_CSRBB | Live on ALM Core | CSRBB quarterly Valuation | Singapore_CSRBB | Live on ALM Core | CSRBB quarterly Valuation | Shanghai_CSRBB | Live on ALM Core | CSRBB quarterly Valuation | Tokyo_CSRBB | Live on ALM Core | Light Maintenance...</v>
+        <v>Light Maintenance | CSRBB quarterly Valuation | Singapore | Live on ALM Core | CSRBB quarterly Valuation | Hong_Kong | Live on ALM Core | CSRBB quarterly Valuation | Sofia | Live on ALM Core | CSRBB quarterly Valuation | Prague | Live on ALM Core</v>
       </c>
     </row>
     <row r="43">
@@ -19271,19 +19270,19 @@
         <v>ICDB</v>
       </c>
       <c r="B43" t="str">
-        <v>ICDB MCP ARA</v>
+        <v>CSRBB_Valuation_Qtr_IRRBBCORE_sideloads_MCP 2025Q4</v>
       </c>
       <c r="C43" t="str">
-        <v>Adhoc prefix: ICDB MCP</v>
+        <v>Single-step adhoc</v>
       </c>
       <c r="D43" t="str">
-        <v>2603</v>
+        <v>2512</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F43" t="str">
-        <v>export to ara</v>
+        <v>CSRBB quarterly Valuation | London_CSRBB | Live on ALM Core | CSRBB quarterly Valuation | Singapore_CSRBB | Live on ALM Core | CSRBB quarterly Valuation | Shanghai_CSRBB | Live on ALM Core | CSRBB quarterly Valuation | Tokyo_CSRBB | Live on ALM Core | Light Maintenance...</v>
       </c>
     </row>
     <row r="44">
@@ -19291,19 +19290,19 @@
         <v>ICDB</v>
       </c>
       <c r="B44" t="str">
-        <v>ICDB R2601_1_MCP2512_1_P delete copy port</v>
+        <v>ICDB MCP ARA</v>
       </c>
       <c r="C44" t="str">
-        <v>Adhoc prefix: ICDB R</v>
+        <v>Adhoc prefix: ICDB MCP</v>
       </c>
       <c r="D44" t="str">
-        <v>2512</v>
+        <v>2603</v>
       </c>
       <c r="E44">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>Delete portfolio from | Portfolio Copy | NLWB_Lending | Live on ALM Core | Portfolio Copy | London | Live on ALM Core | Portfolio Copy | Dublin | Live on ALM Core | Portfolio Copy | Singapore | Live on ALM Core...</v>
+        <v>export to ara</v>
       </c>
     </row>
     <row r="45">
@@ -19311,19 +19310,19 @@
         <v>ICDB</v>
       </c>
       <c r="B45" t="str">
-        <v>ICDB_CSRBB_Export_updated</v>
+        <v>ICDB R2601_1_MCP2512_1_P delete copy port</v>
       </c>
       <c r="C45" t="str">
-        <v>Single-step adhoc</v>
+        <v>Adhoc prefix: ICDB R</v>
       </c>
       <c r="D45" t="str">
-        <v>2602</v>
+        <v>2512</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F45" t="str">
-        <v>CSRBB exports</v>
+        <v>Delete portfolio from | Portfolio Copy | NLWB_Lending | Live on ALM Core | Portfolio Copy | London | Live on ALM Core | Portfolio Copy | Dublin | Live on ALM Core | Portfolio Copy | Singapore | Live on ALM Core...</v>
       </c>
     </row>
     <row r="46">
@@ -19331,7 +19330,7 @@
         <v>ICDB</v>
       </c>
       <c r="B46" t="str">
-        <v>ICDB_CSRBB_Export_updated (copy)</v>
+        <v>ICDB_CSRBB_Export_updated</v>
       </c>
       <c r="C46" t="str">
         <v>Single-step adhoc</v>
@@ -19351,19 +19350,19 @@
         <v>ICDB</v>
       </c>
       <c r="B47" t="str">
-        <v>ICDB_CSRBB_Sideloads</v>
+        <v>ICDB_CSRBB_Export_updated (copy)</v>
       </c>
       <c r="C47" t="str">
         <v>Single-step adhoc</v>
       </c>
       <c r="D47" t="str">
-        <v>2512</v>
+        <v>2602</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>CSRBB create portfolio | CSRBB load position | CSRBB portfolio valuation | CSRBB planning analysis</v>
+        <v>CSRBB exports</v>
       </c>
     </row>
     <row r="48">
@@ -19371,7 +19370,7 @@
         <v>ICDB</v>
       </c>
       <c r="B48" t="str">
-        <v>ICDB_CSRBB_Sideloads continuation</v>
+        <v>ICDB_CSRBB_Sideloads</v>
       </c>
       <c r="C48" t="str">
         <v>Single-step adhoc</v>
@@ -19380,10 +19379,10 @@
         <v>2512</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F48" t="str">
-        <v>CSRBB planning analysis</v>
+        <v>CSRBB create portfolio | CSRBB load position | CSRBB portfolio valuation | CSRBB planning analysis</v>
       </c>
     </row>
     <row r="49">
@@ -19391,7 +19390,7 @@
         <v>ICDB</v>
       </c>
       <c r="B49" t="str">
-        <v>ICDB_CSRBB_Sideloads tokyo plan</v>
+        <v>ICDB_CSRBB_Sideloads continuation</v>
       </c>
       <c r="C49" t="str">
         <v>Single-step adhoc</v>
@@ -19411,19 +19410,19 @@
         <v>ICDB</v>
       </c>
       <c r="B50" t="str">
-        <v>ICDB_MCP  CSRBB + Planning</v>
+        <v>ICDB_CSRBB_Sideloads tokyo plan</v>
       </c>
       <c r="C50" t="str">
-        <v>Adhoc prefix: ICDB_MCP</v>
+        <v>Single-step adhoc</v>
       </c>
       <c r="D50" t="str">
-        <v>2602</v>
+        <v>2512</v>
       </c>
       <c r="E50">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>CSRBB Valuation | NLWB_Lending | Live on ALM Core | Super Light Maintenance | CSRBB Valuation | London | Live on ALM Core | CSRBB Valuation | Singapore | Live on ALM Core | CSRBB Valuation | Hong_Kong | Live on ALM Core...</v>
+        <v>CSRBB planning analysis</v>
       </c>
     </row>
     <row r="51">
@@ -19431,7 +19430,7 @@
         <v>ICDB</v>
       </c>
       <c r="B51" t="str">
-        <v>ICDB_MCP  DEL SPREADS MP , CREATION OF PORT</v>
+        <v>ICDB_MCP  CSRBB + Planning</v>
       </c>
       <c r="C51" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19440,10 +19439,10 @@
         <v>2602</v>
       </c>
       <c r="E51">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F51" t="str">
-        <v>Delete portfolio from | load model parameters from | compare model parameters from | Portfolio Copy | NLWB_Lending | Live on ALM Core | Portfolio Copy | London | Live on ALM Core...</v>
+        <v>CSRBB Valuation | NLWB_Lending | Live on ALM Core | Super Light Maintenance | CSRBB Valuation | London | Live on ALM Core | CSRBB Valuation | Singapore | Live on ALM Core | CSRBB Valuation | Hong_Kong | Live on ALM Core...</v>
       </c>
     </row>
     <row r="52">
@@ -19451,7 +19450,7 @@
         <v>ICDB</v>
       </c>
       <c r="B52" t="str">
-        <v>ICDB_MCP  Load - copywor - Valuation Live locations</v>
+        <v>ICDB_MCP  DEL SPREADS MP , CREATION OF PORT</v>
       </c>
       <c r="C52" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19460,10 +19459,10 @@
         <v>2602</v>
       </c>
       <c r="E52">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F52" t="str">
-        <v>Load | NLWB_Lending | Live on ALM Core | Load | London | Live on ALM Core | Load | Dublin | Live on ALM Core | Load | Singapore | Live on ALM Core | Load | Hong_Kong | Live on ALM Core...</v>
+        <v>Delete portfolio from | load model parameters from | compare model parameters from | Portfolio Copy | NLWB_Lending | Live on ALM Core | Portfolio Copy | London | Live on ALM Core...</v>
       </c>
     </row>
     <row r="53">
@@ -19471,7 +19470,7 @@
         <v>ICDB</v>
       </c>
       <c r="B53" t="str">
-        <v>ICDB_MCP  LOAD + Valuation Other live locations</v>
+        <v>ICDB_MCP  Load - copywor - Valuation Live locations</v>
       </c>
       <c r="C53" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19480,10 +19479,10 @@
         <v>2602</v>
       </c>
       <c r="E53">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="F53" t="str">
-        <v>Load | Shanghai | Other live location | Load | Manila | Other live location | Load | Seoul_Securities | Non-live location | Load | Geneva | Other live location | Portfolio Valuation | Shanghai | Other live location...</v>
+        <v>Load | NLWB_Lending | Live on ALM Core | Load | London | Live on ALM Core | Load | Dublin | Live on ALM Core | Load | Singapore | Live on ALM Core | Load | Hong_Kong | Live on ALM Core...</v>
       </c>
     </row>
     <row r="54">
@@ -19491,7 +19490,7 @@
         <v>ICDB</v>
       </c>
       <c r="B54" t="str">
-        <v>ICDB_MCP  Planning Other live location + ALL GAP, KR, EC</v>
+        <v>ICDB_MCP  LOAD + Valuation Other live locations</v>
       </c>
       <c r="C54" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19500,10 +19499,10 @@
         <v>2602</v>
       </c>
       <c r="E54">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="F54" t="str">
-        <v>planning | Shanghai | Other live location | planning | Manila | Other live location | planning | Seoul_Securities | Non-live location | planning | Geneva | Other live location | gap run | NLWB_Lending | Live on ALM Core...</v>
+        <v>Load | Shanghai | Other live location | Load | Manila | Other live location | Load | Seoul_Securities | Non-live location | Load | Geneva | Other live location | Portfolio Valuation | Shanghai | Other live location...</v>
       </c>
     </row>
     <row r="55">
@@ -19511,7 +19510,7 @@
         <v>ICDB</v>
       </c>
       <c r="B55" t="str">
-        <v>ICDB_MCP  Rerun GPC locations</v>
+        <v>ICDB_MCP  Planning Other live location + ALL GAP, KR, EC</v>
       </c>
       <c r="C55" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19520,10 +19519,10 @@
         <v>2602</v>
       </c>
       <c r="E55">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="F55" t="str">
-        <v>Load | London | Live on ALM Core | Load | Singapore | Live on ALM Core | Load | Hong_Kong | Live on ALM Core | Load | Sofia | Live on ALM Core | Load | Prague | Live on ALM Core...</v>
+        <v>planning | Shanghai | Other live location | planning | Manila | Other live location | planning | Seoul_Securities | Non-live location | planning | Geneva | Other live location | gap run | NLWB_Lending | Live on ALM Core...</v>
       </c>
     </row>
     <row r="56">
@@ -19531,7 +19530,7 @@
         <v>ICDB</v>
       </c>
       <c r="B56" t="str">
-        <v xml:space="preserve">ICDB_MCP  Rerun GPC locations </v>
+        <v>ICDB_MCP  Rerun GPC locations</v>
       </c>
       <c r="C56" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19540,10 +19539,10 @@
         <v>2602</v>
       </c>
       <c r="E56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F56" t="str">
-        <v>Load | Budapest | Live on ALM Core | Load | Tokyo | Live on ALM Core | Load | Bratislava | Live on ALM Core | Load | Seoul | Live on ALM Core | Load | Taipei | Live on ALM Core...</v>
+        <v>Load | London | Live on ALM Core | Load | Singapore | Live on ALM Core | Load | Hong_Kong | Live on ALM Core | Load | Sofia | Live on ALM Core | Load | Prague | Live on ALM Core...</v>
       </c>
     </row>
     <row r="57">
@@ -19551,7 +19550,7 @@
         <v>ICDB</v>
       </c>
       <c r="B57" t="str">
-        <v>ICDB_MCP  Rerun GPC locations beijing + non live load, val, plan</v>
+        <v xml:space="preserve">ICDB_MCP  Rerun GPC locations </v>
       </c>
       <c r="C57" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19560,10 +19559,10 @@
         <v>2602</v>
       </c>
       <c r="E57">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F57" t="str">
-        <v>Load | Beijing | Other live location | Load | Shanghai | Other live location | Load | Manila | Other live location | Portfolio Valuation | Beijing | Other live location | Super Light Maintenance...</v>
+        <v>Load | Budapest | Live on ALM Core | Load | Tokyo | Live on ALM Core | Load | Bratislava | Live on ALM Core | Load | Seoul | Live on ALM Core | Load | Taipei | Live on ALM Core...</v>
       </c>
     </row>
     <row r="58">
@@ -19571,7 +19570,7 @@
         <v>ICDB</v>
       </c>
       <c r="B58" t="str">
-        <v>ICDB_MCP  Rerun GPC locations GAP KR EC</v>
+        <v>ICDB_MCP  Rerun GPC locations beijing + non live load, val, plan</v>
       </c>
       <c r="C58" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19580,10 +19579,10 @@
         <v>2602</v>
       </c>
       <c r="E58">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="F58" t="str">
-        <v>gap run | London | Live on ALM Core | gap run | Singapore | Live on ALM Core | gap run | Hong_Kong | Live on ALM Core | gap run | Sofia | Live on ALM Core | gap run | Prague | Live on ALM Core...</v>
+        <v>Load | Beijing | Other live location | Load | Shanghai | Other live location | Load | Manila | Other live location | Portfolio Valuation | Beijing | Other live location | Super Light Maintenance...</v>
       </c>
     </row>
     <row r="59">
@@ -19591,7 +19590,7 @@
         <v>ICDB</v>
       </c>
       <c r="B59" t="str">
-        <v>ICDB_MCP  Rerun GPC locations val</v>
+        <v>ICDB_MCP  Rerun GPC locations GAP KR EC</v>
       </c>
       <c r="C59" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19600,10 +19599,10 @@
         <v>2602</v>
       </c>
       <c r="E59">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F59" t="str">
-        <v>Portfolio Valuation | London | Live on ALM Core | Super Light Maintenance | Portfolio Valuation | Singapore | Live on ALM Core | Portfolio Valuation | Hong_Kong | Live on ALM Core | Portfolio Valuation | Sofia | Live on ALM Core...</v>
+        <v>gap run | London | Live on ALM Core | gap run | Singapore | Live on ALM Core | gap run | Hong_Kong | Live on ALM Core | gap run | Sofia | Live on ALM Core | gap run | Prague | Live on ALM Core...</v>
       </c>
     </row>
     <row r="60">
@@ -19611,19 +19610,19 @@
         <v>ICDB</v>
       </c>
       <c r="B60" t="str">
-        <v>ICDB_MCP 202601 copy db + Valuation live locations</v>
+        <v>ICDB_MCP  Rerun GPC locations val</v>
       </c>
       <c r="C60" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
       </c>
       <c r="D60" t="str">
-        <v>2601</v>
+        <v>2602</v>
       </c>
       <c r="E60">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F60" t="str">
-        <v>copy from | Portfolio Valuation | NLWB_Lending | Live on ALM Core | Super Light Maintenance | Portfolio Valuation | London | Live on ALM Core | Portfolio Valuation | Dublin | Live on ALM Core...</v>
+        <v>Portfolio Valuation | London | Live on ALM Core | Super Light Maintenance | Portfolio Valuation | Singapore | Live on ALM Core | Portfolio Valuation | Hong_Kong | Live on ALM Core | Portfolio Valuation | Sofia | Live on ALM Core...</v>
       </c>
     </row>
     <row r="61">
@@ -19631,7 +19630,7 @@
         <v>ICDB</v>
       </c>
       <c r="B61" t="str">
-        <v>ICDB_MCP 202601 CSRBB + planning run live locations</v>
+        <v>ICDB_MCP 202601 copy db + Valuation live locations</v>
       </c>
       <c r="C61" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19640,10 +19639,10 @@
         <v>2601</v>
       </c>
       <c r="E61">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F61" t="str">
-        <v>CSRBB Valuation | NLWB_Lending | Live on ALM Core | Super Light Maintenance | CSRBB Valuation | London | Live on ALM Core | CSRBB Valuation | Singapore | Live on ALM Core | CSRBB Valuation | Hong_Kong | Live on ALM Core...</v>
+        <v>copy from | Portfolio Valuation | NLWB_Lending | Live on ALM Core | Super Light Maintenance | Portfolio Valuation | London | Live on ALM Core | Portfolio Valuation | Dublin | Live on ALM Core...</v>
       </c>
     </row>
     <row r="62">
@@ -19651,7 +19650,7 @@
         <v>ICDB</v>
       </c>
       <c r="B62" t="str">
-        <v>ICDB_MCP 202601 CSRBB + planning run live locations rr</v>
+        <v>ICDB_MCP 202601 CSRBB + planning run live locations</v>
       </c>
       <c r="C62" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19660,10 +19659,10 @@
         <v>2601</v>
       </c>
       <c r="E62">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F62" t="str">
-        <v>CSRBB planning | Hong_Kong | Live on ALM Core | CSRBB planning | Sofia | Live on ALM Core | CSRBB planning | Prague | Live on ALM Core | CSRBB planning | Brussels | Live on ALM Core | planning | NLWB_Lending | Live on ALM Core...</v>
+        <v>CSRBB Valuation | NLWB_Lending | Live on ALM Core | Super Light Maintenance | CSRBB Valuation | London | Live on ALM Core | CSRBB Valuation | Singapore | Live on ALM Core | CSRBB Valuation | Hong_Kong | Live on ALM Core...</v>
       </c>
     </row>
     <row r="63">
@@ -19671,7 +19670,7 @@
         <v>ICDB</v>
       </c>
       <c r="B63" t="str">
-        <v>ICDB_MCP 202601 DEL,MP, Spreads, copy port</v>
+        <v>ICDB_MCP 202601 CSRBB + planning run live locations rr</v>
       </c>
       <c r="C63" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19680,10 +19679,10 @@
         <v>2601</v>
       </c>
       <c r="E63">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F63" t="str">
-        <v>Delete portfolio from | load model parameters from | compare model parameters from | Portfolio Copy | NLWB_Lending | Live on ALM Core | Portfolio Copy | London | Live on ALM Core...</v>
+        <v>CSRBB planning | Hong_Kong | Live on ALM Core | CSRBB planning | Sofia | Live on ALM Core | CSRBB planning | Prague | Live on ALM Core | CSRBB planning | Brussels | Live on ALM Core | planning | NLWB_Lending | Live on ALM Core...</v>
       </c>
     </row>
     <row r="64">
@@ -19691,7 +19690,7 @@
         <v>ICDB</v>
       </c>
       <c r="B64" t="str">
-        <v>ICDB_MCP 202601 GAP</v>
+        <v>ICDB_MCP 202601 DEL,MP, Spreads, copy port</v>
       </c>
       <c r="C64" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19700,10 +19699,10 @@
         <v>2601</v>
       </c>
       <c r="E64">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F64" t="str">
-        <v>gap run | NLWB_Lending | Live on ALM Core | gap run | London | Live on ALM Core | gap run | Dublin | Live on ALM Core | gap run | Singapore | Live on ALM Core | gap run | Hong_Kong | Live on ALM Core...</v>
+        <v>Delete portfolio from | load model parameters from | compare model parameters from | Portfolio Copy | NLWB_Lending | Live on ALM Core | Portfolio Copy | London | Live on ALM Core...</v>
       </c>
     </row>
     <row r="65">
@@ -19711,7 +19710,7 @@
         <v>ICDB</v>
       </c>
       <c r="B65" t="str">
-        <v>ICDB_MCP 202601 KR EC</v>
+        <v>ICDB_MCP 202601 GAP</v>
       </c>
       <c r="C65" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19720,10 +19719,10 @@
         <v>2601</v>
       </c>
       <c r="E65">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="F65" t="str">
-        <v>BPV KR valuation | NLWB_Lending | Live on ALM Core | Super Light Maintenance | BPV KR valuation | London | Live on ALM Core | BPV KR valuation | Dublin | Live on ALM Core | BPV KR valuation | false | Live on ALM Core...</v>
+        <v>gap run | NLWB_Lending | Live on ALM Core | gap run | London | Live on ALM Core | gap run | Dublin | Live on ALM Core | gap run | Singapore | Live on ALM Core | gap run | Hong_Kong | Live on ALM Core...</v>
       </c>
     </row>
     <row r="66">
@@ -19731,7 +19730,7 @@
         <v>ICDB</v>
       </c>
       <c r="B66" t="str">
-        <v>ICDB_MCP 202601 load + valuation + planning other live locations</v>
+        <v>ICDB_MCP 202601 KR EC</v>
       </c>
       <c r="C66" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19740,10 +19739,10 @@
         <v>2601</v>
       </c>
       <c r="E66">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="F66" t="str">
-        <v>Load | Beijing | Other live location | Load | Shanghai | Other live location | Load | Manila | Other live location | Load | Geneva | Other live location | Portfolio Valuation | Beijing | Other live location...</v>
+        <v>BPV KR valuation | NLWB_Lending | Live on ALM Core | Super Light Maintenance | BPV KR valuation | London | Live on ALM Core | BPV KR valuation | Dublin | Live on ALM Core | BPV KR valuation | false | Live on ALM Core...</v>
       </c>
     </row>
     <row r="67">
@@ -19751,7 +19750,7 @@
         <v>ICDB</v>
       </c>
       <c r="B67" t="str">
-        <v>ICDB_MCP 202601 load pos live locations part 1</v>
+        <v>ICDB_MCP 202601 load + valuation + planning other live locations</v>
       </c>
       <c r="C67" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19760,10 +19759,10 @@
         <v>2601</v>
       </c>
       <c r="E67">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F67" t="str">
-        <v>Load | NLWB_Lending | Live on ALM Core | Load | London | Live on ALM Core | Load | Dublin | Live on ALM Core | Load | Singapore | Live on ALM Core | Load | Vienna | Live on ALM Core...</v>
+        <v>Load | Beijing | Other live location | Load | Shanghai | Other live location | Load | Manila | Other live location | Load | Geneva | Other live location | Portfolio Valuation | Beijing | Other live location...</v>
       </c>
     </row>
     <row r="68">
@@ -19771,7 +19770,7 @@
         <v>ICDB</v>
       </c>
       <c r="B68" t="str">
-        <v xml:space="preserve">ICDB_MCP 202601 load pos live locations part 2 Banking books </v>
+        <v>ICDB_MCP 202601 load pos live locations part 1</v>
       </c>
       <c r="C68" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19780,10 +19779,10 @@
         <v>2601</v>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F68" t="str">
-        <v>Load | NLWB_FM_Banking_books | Live on ALM Core | Load | Belgium_FM_banking_book | Live on ALM Core</v>
+        <v>Load | NLWB_Lending | Live on ALM Core | Load | London | Live on ALM Core | Load | Dublin | Live on ALM Core | Load | Singapore | Live on ALM Core | Load | Vienna | Live on ALM Core...</v>
       </c>
     </row>
     <row r="69">
@@ -19791,7 +19790,7 @@
         <v>ICDB</v>
       </c>
       <c r="B69" t="str">
-        <v xml:space="preserve">ICDB_MCP 202601 load pos live locations part 3 HK, sofia, kiev </v>
+        <v>ICDB_MCP 202601 load pos live locations part 2 Banking books</v>
       </c>
       <c r="C69" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19800,10 +19799,10 @@
         <v>2601</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F69" t="str">
-        <v>Load | Hong_Kong | Live on ALM Core | Load | Sofia | Live on ALM Core | Load | Kiev | Live on ALM Core</v>
+        <v>Load | NLWB_FM_Banking_books | Live on ALM Core | Load | Belgium_FM_banking_book | Live on ALM Core</v>
       </c>
     </row>
     <row r="70">
@@ -19811,7 +19810,7 @@
         <v>ICDB</v>
       </c>
       <c r="B70" t="str">
-        <v>ICDB_MCP 202601 NII Manila onwards</v>
+        <v>ICDB_MCP 202601 load pos live locations part 3 HK, sofia, kiev</v>
       </c>
       <c r="C70" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19823,7 +19822,7 @@
         <v>3</v>
       </c>
       <c r="F70" t="str">
-        <v>planning | Manila | Other live location | planning | Geneva | Other live location | export to ara</v>
+        <v>Load | Hong_Kong | Live on ALM Core | Load | Sofia | Live on ALM Core | Load | Kiev | Live on ALM Core</v>
       </c>
     </row>
     <row r="71">
@@ -19831,7 +19830,7 @@
         <v>ICDB</v>
       </c>
       <c r="B71" t="str">
-        <v>ICDB_MCP 202601 Valuation_AIC_IRRBBCORE_MCP</v>
+        <v>ICDB_MCP 202601 NII Manila onwards</v>
       </c>
       <c r="C71" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19840,10 +19839,10 @@
         <v>2601</v>
       </c>
       <c r="E71">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F71" t="str">
-        <v>load AIC Spreads | Valuation AIC | NLWB_Lending | Live on ALM Core | Valuation AIC | NLWB_FM_Banking_books | Live on ALM Core | Valuation AIC | NLWB_BMG | Live on ALM Core | Valuation AIC | NLWB_Trade_Finance_Services | Live on ALM Core...</v>
+        <v>planning | Manila | Other live location | planning | Geneva | Other live location | export to ara</v>
       </c>
     </row>
     <row r="72">
@@ -19851,19 +19850,19 @@
         <v>ICDB</v>
       </c>
       <c r="B72" t="str">
-        <v>ICDB_MCP DEL SPREADS MP Copy Portfolio + LOAD + VAL  LIVE LOC</v>
+        <v>ICDB_MCP 202601 Valuation_AIC_IRRBBCORE_MCP</v>
       </c>
       <c r="C72" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
       </c>
       <c r="D72" t="str">
-        <v>2603</v>
+        <v>2601</v>
       </c>
       <c r="E72">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="F72" t="str">
-        <v>Delete portfolio from | load model parameters from | compare model parameters from | Portfolio Copy | NLWB_Lending | Live on ALM Core | Portfolio Copy | London | Live on ALM Core...</v>
+        <v>load AIC Spreads | Valuation AIC | NLWB_Lending | Live on ALM Core | Valuation AIC | NLWB_FM_Banking_books | Live on ALM Core | Valuation AIC | NLWB_BMG | Live on ALM Core | Valuation AIC | NLWB_Trade_Finance_Services | Live on ALM Core...</v>
       </c>
     </row>
     <row r="73">
@@ -19871,7 +19870,7 @@
         <v>ICDB</v>
       </c>
       <c r="B73" t="str">
-        <v>ICDB_MCP Planning LIVE</v>
+        <v>ICDB_MCP DEL SPREADS MP Copy Portfolio + LOAD + VAL  LIVE LOC</v>
       </c>
       <c r="C73" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19880,10 +19879,10 @@
         <v>2603</v>
       </c>
       <c r="E73">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F73" t="str">
-        <v>planning | NLWB_Lending | Live on ALM Core | planning | London | Live on ALM Core | planning | Dublin | Live on ALM Core | planning | Singapore | Live on ALM Core | planning | Hong_Kong | Live on ALM Core...</v>
+        <v>Delete portfolio from | load model parameters from | compare model parameters from | Portfolio Copy | NLWB_Lending | Live on ALM Core | Portfolio Copy | London | Live on ALM Core...</v>
       </c>
     </row>
     <row r="74">
@@ -19891,19 +19890,19 @@
         <v>ICDB</v>
       </c>
       <c r="B74" t="str">
-        <v>ICDB_MCP Valuation AIC</v>
+        <v>ICDB_MCP Planning LIVE</v>
       </c>
       <c r="C74" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
       </c>
       <c r="D74" t="str">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="F74" t="str">
-        <v>load AIC Spreads | Valuation AIC | NLWB_Lending | Live on ALM Core</v>
+        <v>planning | NLWB_Lending | Live on ALM Core | planning | London | Live on ALM Core | planning | Dublin | Live on ALM Core | planning | Singapore | Live on ALM Core | planning | Hong_Kong | Live on ALM Core...</v>
       </c>
     </row>
     <row r="75">
@@ -19911,7 +19910,7 @@
         <v>ICDB</v>
       </c>
       <c r="B75" t="str">
-        <v>ICDB_MCP Valuation AIC rr</v>
+        <v>ICDB_MCP Valuation AIC</v>
       </c>
       <c r="C75" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19931,7 +19930,7 @@
         <v>ICDB</v>
       </c>
       <c r="B76" t="str">
-        <v>ICDB_MCP Valuation AIC rr2</v>
+        <v>ICDB_MCP Valuation AIC rr</v>
       </c>
       <c r="C76" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19951,7 +19950,7 @@
         <v>ICDB</v>
       </c>
       <c r="B77" t="str">
-        <v>ICDB_MCP Valuation AIC rr3</v>
+        <v>ICDB_MCP Valuation AIC rr2</v>
       </c>
       <c r="C77" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19971,7 +19970,7 @@
         <v>ICDB</v>
       </c>
       <c r="B78" t="str">
-        <v>ICDB_MCP Valuation AIC rr4</v>
+        <v>ICDB_MCP Valuation AIC rr3</v>
       </c>
       <c r="C78" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -19991,7 +19990,7 @@
         <v>ICDB</v>
       </c>
       <c r="B79" t="str">
-        <v>ICDB_MCP Valuation AIC rr5</v>
+        <v>ICDB_MCP Valuation AIC rr4</v>
       </c>
       <c r="C79" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -20011,7 +20010,7 @@
         <v>ICDB</v>
       </c>
       <c r="B80" t="str">
-        <v>ICDB_MCP Valuation AIC rr6</v>
+        <v>ICDB_MCP Valuation AIC rr5</v>
       </c>
       <c r="C80" t="str">
         <v>Adhoc prefix: ICDB_MCP</v>
@@ -20020,10 +20019,10 @@
         <v>2602</v>
       </c>
       <c r="E80">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F80" t="str">
-        <v>load AIC Spreads | Valuation AIC | NLWB_Lending | Live on ALM Core | Valuation AIC | NLWB_FM_Banking_books | Live on ALM Core | Valuation AIC | NLWB_BMG | Live on ALM Core | Valuation AIC | NLWB_Trade_Finance_Services | Live on ALM Core...</v>
+        <v>load AIC Spreads | Valuation AIC | NLWB_Lending | Live on ALM Core</v>
       </c>
     </row>
     <row r="81">
@@ -20031,19 +20030,19 @@
         <v>ICDB</v>
       </c>
       <c r="B81" t="str">
-        <v>ICDB_R2601_1_MCP2512_1_P CSRBB VAL AND PLAN</v>
+        <v>ICDB_MCP Valuation AIC rr6</v>
       </c>
       <c r="C81" t="str">
-        <v>Single-step adhoc</v>
+        <v>Adhoc prefix: ICDB_MCP</v>
       </c>
       <c r="D81" t="str">
-        <v>2512</v>
+        <v>2602</v>
       </c>
       <c r="E81">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F81" t="str">
-        <v>CSRBB Valuation | NLWB_Lending | Live on ALM Core | Super Light Maintenance | CSRBB Valuation | London | Live on ALM Core | CSRBB Valuation | Singapore | Live on ALM Core | CSRBB Valuation | Hong_Kong | Live on ALM Core...</v>
+        <v>load AIC Spreads | Valuation AIC | NLWB_Lending | Live on ALM Core | Valuation AIC | NLWB_FM_Banking_books | Live on ALM Core | Valuation AIC | NLWB_BMG | Live on ALM Core | Valuation AIC | NLWB_Trade_Finance_Services | Live on ALM Core...</v>
       </c>
     </row>
     <row r="82">
@@ -20051,7 +20050,7 @@
         <v>ICDB</v>
       </c>
       <c r="B82" t="str">
-        <v>ICDB_R2601_1_MCP2512_1_P Full rerun remaining 9 loc</v>
+        <v>ICDB_R2601_1_MCP2512_1_P CSRBB VAL AND PLAN</v>
       </c>
       <c r="C82" t="str">
         <v>Single-step adhoc</v>
@@ -20060,10 +20059,10 @@
         <v>2512</v>
       </c>
       <c r="E82">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F82" t="str">
-        <v>Load | Hong_Kong | Live on ALM Core | Load | Sofia | Live on ALM Core | Load | Prague | Live on ALM Core | Load | Shanghai | Other live location | Load | Budapest | Live on ALM Core...</v>
+        <v>CSRBB Valuation | NLWB_Lending | Live on ALM Core | Super Light Maintenance | CSRBB Valuation | London | Live on ALM Core | CSRBB Valuation | Singapore | Live on ALM Core | CSRBB Valuation | Hong_Kong | Live on ALM Core...</v>
       </c>
     </row>
     <row r="83">
@@ -20071,7 +20070,7 @@
         <v>ICDB</v>
       </c>
       <c r="B83" t="str">
-        <v>ICDB_R2601_1_MCP2512_1_P Full rerun remaining 9 loc seoul load</v>
+        <v>ICDB_R2601_1_MCP2512_1_P Full rerun remaining 9 loc</v>
       </c>
       <c r="C83" t="str">
         <v>Single-step adhoc</v>
@@ -20080,10 +20079,10 @@
         <v>2512</v>
       </c>
       <c r="E83">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="F83" t="str">
-        <v>Load | Seoul | Live on ALM Core | Load | Taipei | Live on ALM Core | Portfolio Valuation | Hong_Kong | Live on ALM Core | Super Light Maintenance | Portfolio Valuation | Sofia | Live on ALM Core...</v>
+        <v>Load | Hong_Kong | Live on ALM Core | Load | Sofia | Live on ALM Core | Load | Prague | Live on ALM Core | Load | Shanghai | Other live location | Load | Budapest | Live on ALM Core...</v>
       </c>
     </row>
     <row r="84">
@@ -20091,7 +20090,7 @@
         <v>ICDB</v>
       </c>
       <c r="B84" t="str">
-        <v>ICDB_R2601_1_MCP2512_1_P Full rerun SGP priority</v>
+        <v>ICDB_R2601_1_MCP2512_1_P Full rerun remaining 9 loc seoul load</v>
       </c>
       <c r="C84" t="str">
         <v>Single-step adhoc</v>
@@ -20100,10 +20099,10 @@
         <v>2512</v>
       </c>
       <c r="E84">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="F84" t="str">
-        <v>Load | Singapore | Live on ALM Core | Portfolio Valuation | Singapore | Live on ALM Core | Super Light Maintenance | CSRBB Valuation | Singapore | Live on ALM Core | CSRBB planning | Singapore | Live on ALM Core...</v>
+        <v>Load | Seoul | Live on ALM Core | Load | Taipei | Live on ALM Core | Portfolio Valuation | Hong_Kong | Live on ALM Core | Super Light Maintenance | Portfolio Valuation | Sofia | Live on ALM Core...</v>
       </c>
     </row>
     <row r="85">
@@ -20111,7 +20110,7 @@
         <v>ICDB</v>
       </c>
       <c r="B85" t="str">
-        <v>ICDB_R2601_1_MCP2512_1_P ITS GAP</v>
+        <v>ICDB_R2601_1_MCP2512_1_P Full rerun SGP priority</v>
       </c>
       <c r="C85" t="str">
         <v>Single-step adhoc</v>
@@ -20120,10 +20119,10 @@
         <v>2512</v>
       </c>
       <c r="E85">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F85" t="str">
-        <v>GAP ITS run</v>
+        <v>Load | Singapore | Live on ALM Core | Portfolio Valuation | Singapore | Live on ALM Core | Super Light Maintenance | CSRBB Valuation | Singapore | Live on ALM Core | CSRBB planning | Singapore | Live on ALM Core...</v>
       </c>
     </row>
     <row r="86">
@@ -20131,7 +20130,7 @@
         <v>ICDB</v>
       </c>
       <c r="B86" t="str">
-        <v>ICDB_R2601_1_MCP2512_1_P ITS GAP rr + continuation</v>
+        <v>ICDB_R2601_1_MCP2512_1_P ITS GAP</v>
       </c>
       <c r="C86" t="str">
         <v>Single-step adhoc</v>
@@ -20151,7 +20150,7 @@
         <v>ICDB</v>
       </c>
       <c r="B87" t="str">
-        <v>ICDB_R2601_1_MCP2512_1_P Kiev only load pos val</v>
+        <v>ICDB_R2601_1_MCP2512_1_P ITS GAP rr + continuation</v>
       </c>
       <c r="C87" t="str">
         <v>Single-step adhoc</v>
@@ -20160,10 +20159,10 @@
         <v>2512</v>
       </c>
       <c r="E87">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F87" t="str">
-        <v>Load | Kiev | Live on ALM Core | Portfolio Valuation | Kiev | Live on ALM Core | Super Light Maintenance | export to ara</v>
+        <v>GAP ITS run</v>
       </c>
     </row>
     <row r="88">
@@ -20171,7 +20170,7 @@
         <v>ICDB</v>
       </c>
       <c r="B88" t="str">
-        <v>ICDB_R2601_1_MCP2512_1_P Kiev only nii gap kr ec</v>
+        <v>ICDB_R2601_1_MCP2512_1_P Kiev only load pos val</v>
       </c>
       <c r="C88" t="str">
         <v>Single-step adhoc</v>
@@ -20180,10 +20179,10 @@
         <v>2512</v>
       </c>
       <c r="E88">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F88" t="str">
-        <v>planning | Kiev | Live on ALM Core | gap run | Kiev | Live on ALM Core | BPV KR valuation | Kiev | Live on ALM Core | Super Light Maintenance | EC valuation | Kiev | Live on ALM Core...</v>
+        <v>Load | Kiev | Live on ALM Core | Portfolio Valuation | Kiev | Live on ALM Core | Super Light Maintenance | export to ara</v>
       </c>
     </row>
     <row r="89">
@@ -20191,7 +20190,7 @@
         <v>ICDB</v>
       </c>
       <c r="B89" t="str">
-        <v>ICDB_R2601_1_MCP2512_1_P LIVE GAP KR EC exc Kiev</v>
+        <v>ICDB_R2601_1_MCP2512_1_P Kiev only nii gap kr ec</v>
       </c>
       <c r="C89" t="str">
         <v>Single-step adhoc</v>
@@ -20200,10 +20199,10 @@
         <v>2512</v>
       </c>
       <c r="E89">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="F89" t="str">
-        <v>gap run | NLWB_Lending | Live on ALM Core | gap run | London | Live on ALM Core | gap run | Dublin | Live on ALM Core | gap run | Singapore | Live on ALM Core | gap run | Hong_Kong | Live on ALM Core...</v>
+        <v>planning | Kiev | Live on ALM Core | gap run | Kiev | Live on ALM Core | BPV KR valuation | Kiev | Live on ALM Core | Super Light Maintenance | EC valuation | Kiev | Live on ALM Core...</v>
       </c>
     </row>
     <row r="90">
@@ -20211,7 +20210,7 @@
         <v>ICDB</v>
       </c>
       <c r="B90" t="str">
-        <v>ICDB_R2601_1_MCP2512_1_P LIVE load pos and val exc lending and kiev</v>
+        <v>ICDB_R2601_1_MCP2512_1_P LIVE GAP KR EC exc Kiev</v>
       </c>
       <c r="C90" t="str">
         <v>Single-step adhoc</v>
@@ -20220,10 +20219,10 @@
         <v>2512</v>
       </c>
       <c r="E90">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F90" t="str">
-        <v>Load | London | Live on ALM Core | Load | Dublin | Live on ALM Core | Load | Singapore | Live on ALM Core | Load | Hong_Kong | Live on ALM Core | Load | Sofia | Live on ALM Core...</v>
+        <v>gap run | NLWB_Lending | Live on ALM Core | gap run | London | Live on ALM Core | gap run | Dublin | Live on ALM Core | gap run | Singapore | Live on ALM Core | gap run | Hong_Kong | Live on ALM Core...</v>
       </c>
     </row>
     <row r="91">
@@ -20231,7 +20230,7 @@
         <v>ICDB</v>
       </c>
       <c r="B91" t="str">
-        <v>ICDB_R2601_1_MCP2512_1_P load pos val lending only</v>
+        <v>ICDB_R2601_1_MCP2512_1_P LIVE load pos and val exc lending and kiev</v>
       </c>
       <c r="C91" t="str">
         <v>Single-step adhoc</v>
@@ -20240,10 +20239,10 @@
         <v>2512</v>
       </c>
       <c r="E91">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="F91" t="str">
-        <v>Load | NLWB_Lending | Live on ALM Core | Portfolio Valuation | NLWB_Lending | Live on ALM Core | Super Light Maintenance</v>
+        <v>Load | London | Live on ALM Core | Load | Dublin | Live on ALM Core | Load | Singapore | Live on ALM Core | Load | Hong_Kong | Live on ALM Core | Load | Sofia | Live on ALM Core...</v>
       </c>
     </row>
     <row r="92">
@@ -20251,7 +20250,7 @@
         <v>ICDB</v>
       </c>
       <c r="B92" t="str">
-        <v>ICDB_R2601_1_MCP2512_1_P mps and spreads</v>
+        <v>ICDB_R2601_1_MCP2512_1_P load pos val lending only</v>
       </c>
       <c r="C92" t="str">
         <v>Single-step adhoc</v>
@@ -20263,7 +20262,7 @@
         <v>3</v>
       </c>
       <c r="F92" t="str">
-        <v>load spreads from | load model parameters from | compare model parameters from</v>
+        <v>Load | NLWB_Lending | Live on ALM Core | Portfolio Valuation | NLWB_Lending | Live on ALM Core | Super Light Maintenance</v>
       </c>
     </row>
     <row r="93">
@@ -20271,7 +20270,7 @@
         <v>ICDB</v>
       </c>
       <c r="B93" t="str">
-        <v>ICDB_R2601_1_MCP2512_1_P other live pos val nii gap ec kr</v>
+        <v>ICDB_R2601_1_MCP2512_1_P mps and spreads</v>
       </c>
       <c r="C93" t="str">
         <v>Single-step adhoc</v>
@@ -20280,10 +20279,10 @@
         <v>2512</v>
       </c>
       <c r="E93">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="F93" t="str">
-        <v>Load | Beijing | Other live location | Load | Shanghai | Other live location | Load | Manila | Other live location | Load | Geneva | Other live location | Portfolio Valuation | Beijing | Other live location...</v>
+        <v>load spreads from | load model parameters from | compare model parameters from</v>
       </c>
     </row>
     <row r="94">
@@ -20291,7 +20290,7 @@
         <v>ICDB</v>
       </c>
       <c r="B94" t="str">
-        <v>ICDB_R2601_1_MCP2512_1_P PLANNING EXC KIEV</v>
+        <v>ICDB_R2601_1_MCP2512_1_P other live pos val nii gap ec kr</v>
       </c>
       <c r="C94" t="str">
         <v>Single-step adhoc</v>
@@ -20300,10 +20299,10 @@
         <v>2512</v>
       </c>
       <c r="E94">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F94" t="str">
-        <v>planning | NLWB_BMG | Other live location | planning | NLWB_Lending | Live on ALM Core | planning | London | Live on ALM Core | planning | Dublin | Live on ALM Core | planning | Singapore | Live on ALM Core...</v>
+        <v>Load | Beijing | Other live location | Load | Shanghai | Other live location | Load | Manila | Other live location | Load | Geneva | Other live location | Portfolio Valuation | Beijing | Other live location...</v>
       </c>
     </row>
     <row r="95">
@@ -20311,7 +20310,7 @@
         <v>ICDB</v>
       </c>
       <c r="B95" t="str">
-        <v>Valuation_AIC_IRRBBCORE_MCP Brussels only</v>
+        <v>ICDB_R2601_1_MCP2512_1_P PLANNING EXC KIEV</v>
       </c>
       <c r="C95" t="str">
         <v>Single-step adhoc</v>
@@ -20320,10 +20319,10 @@
         <v>2512</v>
       </c>
       <c r="E95">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F95" t="str">
-        <v>Valuation AIC | Brussels | Live on ALM Core</v>
+        <v>planning | NLWB_BMG | Other live location | planning | NLWB_Lending | Live on ALM Core | planning | London | Live on ALM Core | planning | Dublin | Live on ALM Core | planning | Singapore | Live on ALM Core...</v>
       </c>
     </row>
     <row r="96">
@@ -20331,7 +20330,7 @@
         <v>ICDB</v>
       </c>
       <c r="B96" t="str">
-        <v>Valuation_AIC_IRRBBCORE_MCP exc Brussels</v>
+        <v>Valuation_AIC_IRRBBCORE_MCP Brussels only</v>
       </c>
       <c r="C96" t="str">
         <v>Single-step adhoc</v>
@@ -20340,30 +20339,30 @@
         <v>2512</v>
       </c>
       <c r="E96">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F96" t="str">
-        <v>load AIC Spreads | Valuation AIC | NLWB_Lending | Live on ALM Core | Valuation AIC | NLWB_FM_Banking_books | Live on ALM Core | Valuation AIC | NLWB_BMG | Live on ALM Core | Valuation AIC | NLWB_Trade_Finance_Services | Live on ALM Core</v>
+        <v>Valuation AIC | Brussels | Live on ALM Core</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ITDB</v>
+        <v>ICDB</v>
       </c>
       <c r="B97" t="str">
-        <v>Copy_dbwruns_MCP</v>
+        <v>Valuation_AIC_IRRBBCORE_MCP exc Brussels</v>
       </c>
       <c r="C97" t="str">
-        <v>Adhoc prefix: Copy_dbwruns</v>
+        <v>Single-step adhoc</v>
       </c>
       <c r="D97" t="str">
-        <v>2603</v>
+        <v>2512</v>
       </c>
       <c r="E97">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F97" t="str">
-        <v>copy from</v>
+        <v>load AIC Spreads | Valuation AIC | NLWB_Lending | Live on ALM Core | Valuation AIC | NLWB_FM_Banking_books | Live on ALM Core | Valuation AIC | NLWB_BMG | Live on ALM Core | Valuation AIC | NLWB_Trade_Finance_Services | Live on ALM Core</v>
       </c>
     </row>
     <row r="98">
@@ -20371,47 +20370,47 @@
         <v>ITDB</v>
       </c>
       <c r="B98" t="str">
-        <v>GAP_ITS_IT_MCP</v>
+        <v>Copy_dbwruns_MCP</v>
       </c>
       <c r="C98" t="str">
-        <v>Single-step adhoc</v>
+        <v>Adhoc prefix: Copy_dbwruns</v>
       </c>
       <c r="D98" t="str">
-        <v>2512</v>
+        <v>2603</v>
       </c>
       <c r="E98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" t="str">
-        <v>Light Maintenance | GAP ITS planning run</v>
+        <v>copy from</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>LUDB</v>
+        <v>ITDB</v>
       </c>
       <c r="B99" t="str">
-        <v>Copy_dbwruns_MCP</v>
+        <v>GAP_ITS_IT_MCP</v>
       </c>
       <c r="C99" t="str">
-        <v>Adhoc prefix: Copy_dbwruns</v>
+        <v>Single-step adhoc</v>
       </c>
       <c r="D99" t="str">
-        <v>2603</v>
+        <v>2512</v>
       </c>
       <c r="E99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" t="str">
-        <v>copy from</v>
+        <v>Light Maintenance | GAP ITS planning run</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>NLBTR</v>
+        <v>LUDB</v>
       </c>
       <c r="B100" t="str">
-        <v>Copy_dbwruns_NLBTR_MCP</v>
+        <v>Copy_dbwruns_MCP</v>
       </c>
       <c r="C100" t="str">
         <v>Adhoc prefix: Copy_dbwruns</v>
@@ -20431,19 +20430,19 @@
         <v>NLBTR</v>
       </c>
       <c r="B101" t="str">
-        <v>Copy_Portfolio_NLBTR old model</v>
+        <v>Copy_dbwruns_NLBTR_MCP</v>
       </c>
       <c r="C101" t="str">
-        <v>Single-step adhoc</v>
+        <v>Adhoc prefix: Copy_dbwruns</v>
       </c>
       <c r="D101" t="str">
-        <v>2512, 2601</v>
+        <v>2603</v>
       </c>
       <c r="E101">
         <v>1</v>
       </c>
       <c r="F101" t="str">
-        <v>Copy portfolio</v>
+        <v>copy from</v>
       </c>
     </row>
     <row r="102">
@@ -20451,19 +20450,19 @@
         <v>NLBTR</v>
       </c>
       <c r="B102" t="str">
-        <v>Copy_Portfolio_NLBTR_MCP Old Model</v>
+        <v>Copy_Portfolio_NLBTR old model</v>
       </c>
       <c r="C102" t="str">
         <v>Single-step adhoc</v>
       </c>
       <c r="D102" t="str">
-        <v>2602</v>
+        <v>2512, 2601</v>
       </c>
       <c r="E102">
         <v>1</v>
       </c>
       <c r="F102" t="str">
-        <v>Copy portfolio RAS</v>
+        <v>Copy portfolio</v>
       </c>
     </row>
     <row r="103">
@@ -20471,7 +20470,7 @@
         <v>NLBTR</v>
       </c>
       <c r="B103" t="str">
-        <v>Copy_Portfolio_NLBTR_MCP Old Model rr</v>
+        <v>Copy_Portfolio_NLBTR_MCP Old Model</v>
       </c>
       <c r="C103" t="str">
         <v>Single-step adhoc</v>
@@ -20491,7 +20490,7 @@
         <v>NLBTR</v>
       </c>
       <c r="B104" t="str">
-        <v>Copy_Portfolio_NLBTR_MCP Old to New Model</v>
+        <v>Copy_Portfolio_NLBTR_MCP Old Model rr</v>
       </c>
       <c r="C104" t="str">
         <v>Single-step adhoc</v>
@@ -20511,19 +20510,19 @@
         <v>NLBTR</v>
       </c>
       <c r="B105" t="str">
-        <v>GAP_ITS_NLBTR_MCP</v>
+        <v>Copy_Portfolio_NLBTR_MCP Old to New Model</v>
       </c>
       <c r="C105" t="str">
         <v>Single-step adhoc</v>
       </c>
       <c r="D105" t="str">
-        <v>2512, 2603</v>
+        <v>2602</v>
       </c>
       <c r="E105">
         <v>1</v>
       </c>
       <c r="F105" t="str">
-        <v>GAP ITS planning run</v>
+        <v>Copy portfolio RAS</v>
       </c>
     </row>
     <row r="106">
@@ -20531,19 +20530,19 @@
         <v>NLBTR</v>
       </c>
       <c r="B106" t="str">
-        <v>Load_POS_NLBTR_MCP_RAS</v>
+        <v>GAP_ITS_NLBTR_MCP</v>
       </c>
       <c r="C106" t="str">
-        <v>RAS at NLBTR</v>
+        <v>Single-step adhoc</v>
       </c>
       <c r="D106" t="str">
-        <v>2602</v>
+        <v>2512, 2603</v>
       </c>
       <c r="E106">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F106" t="str">
-        <v>load RAS | Stratification RAS | Light Maintenance RAS | Position report OLAP exports RAS | copy from RAS</v>
+        <v>GAP ITS planning run</v>
       </c>
     </row>
     <row r="107">
@@ -20551,19 +20550,19 @@
         <v>NLBTR</v>
       </c>
       <c r="B107" t="str">
-        <v>LOAD_POS_NLBTR_MCP_RAS</v>
+        <v>Load_POS_NLBTR_MCP_RAS</v>
       </c>
       <c r="C107" t="str">
         <v>RAS at NLBTR</v>
       </c>
       <c r="D107" t="str">
-        <v>2512, 2601, 2602, 2603</v>
+        <v>2602</v>
       </c>
       <c r="E107">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F107" t="str">
-        <v>load RAS | Stratification RAS | Light Maintenance | Position report OLAP exports RAS | copy from...</v>
+        <v>load RAS | Stratification RAS | Light Maintenance RAS | Position report OLAP exports RAS | copy from RAS</v>
       </c>
     </row>
     <row r="108">
@@ -20571,19 +20570,19 @@
         <v>NLBTR</v>
       </c>
       <c r="B108" t="str">
-        <v>LOAD_POS_NLBTR_MCP_RAS rr from line 112 down</v>
+        <v>LOAD_POS_NLBTR_MCP_RAS</v>
       </c>
       <c r="C108" t="str">
         <v>RAS at NLBTR</v>
       </c>
       <c r="D108" t="str">
-        <v>2601</v>
+        <v>2512, 2601, 2602, 2603</v>
       </c>
       <c r="E108">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F108" t="str">
-        <v>Position report OLAP exports RAS | copy from</v>
+        <v>load RAS | Stratification RAS | Light Maintenance | Position report OLAP exports RAS | copy from...</v>
       </c>
     </row>
     <row r="109">
@@ -20591,19 +20590,19 @@
         <v>NLBTR</v>
       </c>
       <c r="B109" t="str">
-        <v>Planning_NLBTR_MCP_RAS</v>
+        <v>LOAD_POS_NLBTR_MCP_RAS rr from line 112 down</v>
       </c>
       <c r="C109" t="str">
         <v>RAS at NLBTR</v>
       </c>
       <c r="D109" t="str">
-        <v>2601, 2602</v>
+        <v>2601</v>
       </c>
       <c r="E109">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F109" t="str">
-        <v>planning run | export to ara | planning run QRM Reporter exports | Full Maintenance | planning run OLAP exports...</v>
+        <v>Position report OLAP exports RAS | copy from</v>
       </c>
     </row>
     <row r="110">
@@ -20611,19 +20610,19 @@
         <v>NLBTR</v>
       </c>
       <c r="B110" t="str">
-        <v>Planning_NLBTR_MCP_RAS rr</v>
+        <v>Planning_NLBTR_MCP_RAS</v>
       </c>
       <c r="C110" t="str">
         <v>RAS at NLBTR</v>
       </c>
       <c r="D110" t="str">
-        <v>2602</v>
+        <v>2601, 2602</v>
       </c>
       <c r="E110">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F110" t="str">
-        <v>planning run OLAP exports RAS</v>
+        <v>planning run | export to ara | planning run QRM Reporter exports | Full Maintenance | planning run OLAP exports...</v>
       </c>
     </row>
     <row r="111">
@@ -20631,7 +20630,7 @@
         <v>NLBTR</v>
       </c>
       <c r="B111" t="str">
-        <v>Planning_NLBTR_MCP_RAS rr2</v>
+        <v>Planning_NLBTR_MCP_RAS rr</v>
       </c>
       <c r="C111" t="str">
         <v>RAS at NLBTR</v>
@@ -20651,39 +20650,39 @@
         <v>NLBTR</v>
       </c>
       <c r="B112" t="str">
-        <v>Valuation_NLBTR_MCP_RAS</v>
+        <v>Planning_NLBTR_MCP_RAS rr2</v>
       </c>
       <c r="C112" t="str">
         <v>RAS at NLBTR</v>
       </c>
       <c r="D112" t="str">
-        <v>2512, 2601, 2602</v>
+        <v>2602</v>
       </c>
       <c r="E112">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F112" t="str">
-        <v>portfolio valuation run RAS | export to ara | Light Maintenance | valuation report exports RAS | AIC portfolio valuation run RAS...</v>
+        <v>planning run OLAP exports RAS</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>NLRB</v>
+        <v>NLBTR</v>
       </c>
       <c r="B113" t="str">
-        <v>Copy_dbwruns_NL_MCP</v>
+        <v>Valuation_NLBTR_MCP_RAS</v>
       </c>
       <c r="C113" t="str">
-        <v>Adhoc prefix: Copy_dbwruns</v>
+        <v>RAS at NLBTR</v>
       </c>
       <c r="D113" t="str">
-        <v>2603</v>
+        <v>2512, 2601, 2602</v>
       </c>
       <c r="E113">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F113" t="str">
-        <v>copy from</v>
+        <v>portfolio valuation run RAS | export to ara | Light Maintenance | valuation report exports RAS | AIC portfolio valuation run RAS...</v>
       </c>
     </row>
     <row r="114">
@@ -20691,39 +20690,39 @@
         <v>NLRB</v>
       </c>
       <c r="B114" t="str">
-        <v>GAP_ITS_NL_MCP</v>
+        <v>Copy_dbwruns_NL_MCP</v>
       </c>
       <c r="C114" t="str">
-        <v>Single-step adhoc</v>
+        <v>Adhoc prefix: Copy_dbwruns</v>
       </c>
       <c r="D114" t="str">
-        <v>2512</v>
+        <v>2603</v>
       </c>
       <c r="E114">
         <v>1</v>
       </c>
       <c r="F114" t="str">
-        <v>GAP ITS planning run</v>
+        <v>copy from</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>PLDB</v>
+        <v>NLRB</v>
       </c>
       <c r="B115" t="str">
-        <v>Copy_dbwruns_MCP</v>
+        <v>GAP_ITS_NL_MCP</v>
       </c>
       <c r="C115" t="str">
-        <v>Adhoc prefix: Copy_dbwruns</v>
+        <v>Single-step adhoc</v>
       </c>
       <c r="D115" t="str">
-        <v>2603</v>
+        <v>2512</v>
       </c>
       <c r="E115">
         <v>1</v>
       </c>
       <c r="F115" t="str">
-        <v>copy from</v>
+        <v>GAP ITS planning run</v>
       </c>
     </row>
     <row r="116">
@@ -20731,19 +20730,19 @@
         <v>PLDB</v>
       </c>
       <c r="B116" t="str">
-        <v>CSRBB_Export</v>
+        <v>Copy_dbwruns_MCP</v>
       </c>
       <c r="C116" t="str">
-        <v>Single-step adhoc</v>
+        <v>Adhoc prefix: Copy_dbwruns</v>
       </c>
       <c r="D116" t="str">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="E116">
         <v>1</v>
       </c>
       <c r="F116" t="str">
-        <v>CSRBB exports</v>
+        <v>copy from</v>
       </c>
     </row>
     <row r="117">
@@ -20751,27 +20750,27 @@
         <v>PLDB</v>
       </c>
       <c r="B117" t="str">
-        <v>GAP_ITS_PL_MCP</v>
+        <v>CSRBB_Export</v>
       </c>
       <c r="C117" t="str">
         <v>Single-step adhoc</v>
       </c>
       <c r="D117" t="str">
-        <v>2512</v>
+        <v>2602</v>
       </c>
       <c r="E117">
         <v>1</v>
       </c>
       <c r="F117" t="str">
-        <v>GAP ITS planning run</v>
+        <v>CSRBB exports</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>TRDB</v>
+        <v>PLDB</v>
       </c>
       <c r="B118" t="str">
-        <v>GAP_ITS_TR_MCP</v>
+        <v>GAP_ITS_PL_MCP</v>
       </c>
       <c r="C118" t="str">
         <v>Single-step adhoc</v>
@@ -20788,22 +20787,22 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>WBUS</v>
+        <v>TRDB</v>
       </c>
       <c r="B119" t="str">
-        <v>CSRBB_Sideload_US_MCP</v>
+        <v>GAP_ITS_TR_MCP</v>
       </c>
       <c r="C119" t="str">
-        <v>Adhoc prefix: CSRBB_Sideload</v>
+        <v>Single-step adhoc</v>
       </c>
       <c r="D119" t="str">
         <v>2512</v>
       </c>
       <c r="E119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F119" t="str">
-        <v>CSRBB Sideload | CSRBB Sideload Portfolio Valuation</v>
+        <v>GAP ITS planning run</v>
       </c>
     </row>
     <row r="120">
@@ -20811,7 +20810,7 @@
         <v>WBUS</v>
       </c>
       <c r="B120" t="str">
-        <v>CSRBB_Sideload_US_MCP rr</v>
+        <v>CSRBB_Sideload_US_MCP</v>
       </c>
       <c r="C120" t="str">
         <v>Adhoc prefix: CSRBB_Sideload</v>
@@ -20820,10 +20819,10 @@
         <v>2512</v>
       </c>
       <c r="E120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" t="str">
-        <v>CSRBB Sideload Portfolio Valuation</v>
+        <v>CSRBB Sideload | CSRBB Sideload Portfolio Valuation</v>
       </c>
     </row>
     <row r="121">
@@ -20831,7 +20830,7 @@
         <v>WBUS</v>
       </c>
       <c r="B121" t="str">
-        <v>CSRBB_Sideload_US_MCP rr2</v>
+        <v>CSRBB_Sideload_US_MCP rr</v>
       </c>
       <c r="C121" t="str">
         <v>Adhoc prefix: CSRBB_Sideload</v>
@@ -20851,7 +20850,7 @@
         <v>WBUS</v>
       </c>
       <c r="B122" t="str">
-        <v>CSRBB_Sideload_US_MCP rr3</v>
+        <v>CSRBB_Sideload_US_MCP rr2</v>
       </c>
       <c r="C122" t="str">
         <v>Adhoc prefix: CSRBB_Sideload</v>
@@ -20871,7 +20870,7 @@
         <v>WBUS</v>
       </c>
       <c r="B123" t="str">
-        <v>CSRBB_Sideload_US_MCP rr4</v>
+        <v>CSRBB_Sideload_US_MCP rr3</v>
       </c>
       <c r="C123" t="str">
         <v>Adhoc prefix: CSRBB_Sideload</v>
@@ -20880,10 +20879,10 @@
         <v>2512</v>
       </c>
       <c r="E123">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F123" t="str">
-        <v>of script | CSRBB Sideload Portfolio Valuation | CSRBB Sideload Planning Run | Light Maintenance | CSRBB Portfolio Valuation Qtr...</v>
+        <v>CSRBB Sideload Portfolio Valuation</v>
       </c>
     </row>
     <row r="124">
@@ -20891,32 +20890,52 @@
         <v>WBUS</v>
       </c>
       <c r="B124" t="str">
-        <v>GAP_ITS_US_MCP</v>
+        <v>CSRBB_Sideload_US_MCP rr4</v>
       </c>
       <c r="C124" t="str">
-        <v>Single-step adhoc</v>
+        <v>Adhoc prefix: CSRBB_Sideload</v>
       </c>
       <c r="D124" t="str">
         <v>2512</v>
       </c>
       <c r="E124">
+        <v>7</v>
+      </c>
+      <c r="F124" t="str">
+        <v>of script | CSRBB Sideload Portfolio Valuation | CSRBB Sideload Planning Run | Light Maintenance | CSRBB Portfolio Valuation Qtr...</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>WBUS</v>
+      </c>
+      <c r="B125" t="str">
+        <v>GAP_ITS_US_MCP</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Single-step adhoc</v>
+      </c>
+      <c r="D125" t="str">
+        <v>2512</v>
+      </c>
+      <c r="E125">
         <v>1</v>
       </c>
-      <c r="F124" t="str">
+      <c r="F125" t="str">
         <v>GAP ITS planning run</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F124"/>
+  <autoFilter ref="A1:F125"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F124"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F125"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E32"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -20950,19 +20969,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>BEDB</v>
+        <v>AUDB</v>
       </c>
       <c r="B2" t="str">
-        <v>Load_Yield_Curves_ATTRIB_BE_MCP</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>2512</v>
+        <v>2601</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="str">
-        <v>Load yield curves -&gt; Load yield curve market 05</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -20970,16 +20989,16 @@
         <v>BEDB</v>
       </c>
       <c r="B3" t="str">
-        <v>Load_Yield_Curves_ATTRIB_BE_MCP rr</v>
+        <v/>
       </c>
       <c r="C3" t="str">
-        <v>2512</v>
+        <v>2601</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3" t="str">
-        <v>Load yield curve market 05 -&gt; Load yield curves -&gt; Load yield curve market 06 -&gt; Copy market 07 -&gt; Load yield curve market 07</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -20987,75 +21006,75 @@
         <v>BEDB</v>
       </c>
       <c r="B4" t="str">
-        <v>Valuations_ATTRIB_BE_MCP</v>
+        <v>Load_Yield_Curves_ATTRIB_BE_MCP</v>
       </c>
       <c r="C4" t="str">
         <v>2512</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E4" t="str">
-        <v>of run 00 -&gt; of run 08 -&gt; of run 01 -&gt; of run 02 -&gt; of run 03 -&gt; of run 04 -&gt; of run 05 -&gt; of run 06 -&gt; of run 07 -&gt; Valuations -&gt; of Light US</v>
+        <v>Load yield curves -&gt; Load yield curve market 05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>BEGT</v>
+        <v>BEDB</v>
       </c>
       <c r="B5" t="str">
-        <v>Load_ARA_ACC_BEGT_MCP</v>
+        <v>Load_Yield_Curves_ATTRIB_BE_MCP rr</v>
       </c>
       <c r="C5" t="str">
-        <v>2603</v>
+        <v>2512</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5" t="str">
-        <v>export to ara ACC</v>
+        <v>Load yield curve market 05 -&gt; Load yield curves -&gt; Load yield curve market 06 -&gt; Copy market 07 -&gt; Load yield curve market 07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>BEGT</v>
+        <v>BEDB</v>
       </c>
       <c r="B6" t="str">
-        <v>Load_ARA_BEGT_MCP</v>
+        <v>Valuations_ATTRIB_BE_MCP</v>
       </c>
       <c r="C6" t="str">
-        <v>2603</v>
+        <v>2512</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E6" t="str">
-        <v>export to ara</v>
+        <v>of run 00 -&gt; of run 08 -&gt; of run 01 -&gt; of run 02 -&gt; of run 03 -&gt; of run 04 -&gt; of run 05 -&gt; of run 06 -&gt; of run 07 -&gt; Valuations -&gt; of Light US</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>DEDB</v>
+        <v>BEGT</v>
       </c>
       <c r="B7" t="str">
-        <v>Load_ARA_DE_MCP</v>
+        <v/>
       </c>
       <c r="C7" t="str">
-        <v>2603</v>
+        <v>2601</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="str">
-        <v>export to ara</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>DEDB</v>
+        <v>BEGT</v>
       </c>
       <c r="B8" t="str">
-        <v>Quarter_Valuation_DE_MCP</v>
+        <v>Load_ARA_ACC_BEGT_MCP</v>
       </c>
       <c r="C8" t="str">
         <v>2603</v>
@@ -21064,49 +21083,49 @@
         <v>1</v>
       </c>
       <c r="E8" t="str">
-        <v>load quarterly spreads</v>
+        <v>export to ara ACC</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>DEDB</v>
+        <v>BEGT</v>
       </c>
       <c r="B9" t="str">
-        <v>Quarter_Valuation_DE_MCP_ESM0534743</v>
+        <v>Load_ARA_BEGT_MCP</v>
       </c>
       <c r="C9" t="str">
-        <v>2512</v>
+        <v>2603</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="str">
-        <v>Light Maintenance</v>
+        <v>export to ara</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>DEGT</v>
+        <v>DEDB</v>
       </c>
       <c r="B10" t="str">
-        <v>Load_ARA_ACC_DEGT_MCP</v>
+        <v/>
       </c>
       <c r="C10" t="str">
-        <v>2603</v>
+        <v>2601</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="str">
-        <v>export to ara ACC</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>DEGT</v>
+        <v>DEDB</v>
       </c>
       <c r="B11" t="str">
-        <v>Load_ARA_DEGT_MCP</v>
+        <v>Load_ARA_DE_MCP</v>
       </c>
       <c r="C11" t="str">
         <v>2603</v>
@@ -21120,10 +21139,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>NLBTR</v>
+        <v>DEDB</v>
       </c>
       <c r="B12" t="str">
-        <v>Load_ARA_ACC_NLBTR_MCP</v>
+        <v>Quarter_Valuation_DE_MCP</v>
       </c>
       <c r="C12" t="str">
         <v>2603</v>
@@ -21132,115 +21151,353 @@
         <v>1</v>
       </c>
       <c r="E12" t="str">
-        <v>export to ara ACC</v>
+        <v>load quarterly spreads</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>NLBTR</v>
+        <v>DEDB</v>
       </c>
       <c r="B13" t="str">
-        <v>Load_ARA_NLBTR_MCP</v>
+        <v>Quarter_Valuation_DE_MCP_ESM0534743</v>
       </c>
       <c r="C13" t="str">
-        <v>2603</v>
+        <v>2512</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" t="str">
-        <v>export to ara</v>
+        <v>Light Maintenance</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>RODB</v>
+        <v>DEGT</v>
       </c>
       <c r="B14" t="str">
-        <v>PROD_LAD_SF_RO (copy 5.0)</v>
+        <v>Load_ARA_ACC_DEGT_MCP</v>
       </c>
       <c r="C14" t="str">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="str">
-        <v>LAD_SF</v>
+        <v>export to ara ACC</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>RODB</v>
+        <v>DEGT</v>
       </c>
       <c r="B15" t="str">
-        <v>PROD_LAD_SF_RO (copy 7.0)</v>
+        <v>Load_ARA_DEGT_MCP</v>
       </c>
       <c r="C15" t="str">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15" t="str">
-        <v>LAD_SF</v>
+        <v>export to ara</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>RODB</v>
+        <v>ESDB</v>
       </c>
       <c r="B16" t="str">
-        <v>PROD_LAD_SF_RO (copy 8.0)</v>
+        <v/>
       </c>
       <c r="C16" t="str">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" t="str">
-        <v>LAD_SF</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>RODB</v>
+        <v>FRDB</v>
       </c>
       <c r="B17" t="str">
-        <v>PROD_LAD_SF_RO (copy 9.0)</v>
+        <v/>
       </c>
       <c r="C17" t="str">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" t="str">
-        <v>LAD_SF</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>TRDB</v>
+        <v>ITDB</v>
       </c>
       <c r="B18" t="str">
-        <v>Load_ARA_TR_MCP</v>
+        <v/>
       </c>
       <c r="C18" t="str">
-        <v>2603</v>
+        <v>2601</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>LUDB</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v>2601</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>NLBTR</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v>2601</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>NLBTR</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Load_ARA_ACC_NLBTR_MCP</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2603</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="str">
+        <v>export to ara ACC</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>NLBTR</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Load_ARA_NLBTR_MCP</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2603</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="str">
         <v>export to ara</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>NLRB</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v>2601</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>PLDB</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v>2601</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>RODB</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v>2601</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>RODB</v>
+      </c>
+      <c r="B26" t="str">
+        <v>PROD_LAD_SF_RO (copy 5.0)</v>
+      </c>
+      <c r="C26" t="str">
+        <v>2602</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="str">
+        <v>LAD_SF</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>RODB</v>
+      </c>
+      <c r="B27" t="str">
+        <v>PROD_LAD_SF_RO (copy 7.0)</v>
+      </c>
+      <c r="C27" t="str">
+        <v>2602</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="str">
+        <v>LAD_SF</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>RODB</v>
+      </c>
+      <c r="B28" t="str">
+        <v>PROD_LAD_SF_RO (copy 8.0)</v>
+      </c>
+      <c r="C28" t="str">
+        <v>2602</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="str">
+        <v>LAD_SF</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>RODB</v>
+      </c>
+      <c r="B29" t="str">
+        <v>PROD_LAD_SF_RO (copy 9.0)</v>
+      </c>
+      <c r="C29" t="str">
+        <v>2602</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="str">
+        <v>LAD_SF</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>TRDB</v>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v>2601</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>TRDB</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Load_ARA_TR_MCP</v>
+      </c>
+      <c r="C31" t="str">
+        <v>2603</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="str">
+        <v>export to ara</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>WBUS</v>
+      </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <v>2601</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E18"/>
+  <autoFilter ref="A1:E32"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E32"/>
   </ignoredErrors>
 </worksheet>
 </file>